--- a/xlsx/AC-F.xlsx
+++ b/xlsx/AC-F.xlsx
@@ -14,8 +14,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AC-F-L3" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AC-F-L4" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AC-F-L5" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_템플릿" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_코드체계" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AC-F-M1" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AC-F-M2" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_템플릿" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_코드체계" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="24">
+  <fonts count="31">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -161,8 +163,46 @@
       <color rgb="FF2C4F29"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF5C4526"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF37505C"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF2E5C42"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF2E5C42"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF2E5C42"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF1C1C1A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF2A5468"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -204,6 +244,26 @@
         <fgColor rgb="FFF7E8EF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1E9DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6EDF1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF2EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3F6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -232,7 +292,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -357,6 +417,34 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -724,7 +812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -948,7 +1036,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>방진고무 장선 부유바닥 (십자패드 + 그린글루)</t>
+          <t>장선 부유바닥 (투바이 28×67 + 십자패드)</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -984,7 +1072,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>방진고무 장선 부유바닥 심층형 (불연)</t>
+          <t>장선 부유바닥 구조재형 (투바이포 38×89 · 불연)</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -1010,75 +1098,113 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="37" t="inlineStr">
+      <c r="A11" s="54" t="inlineStr">
+        <is>
+          <t>AC-F-M1</t>
+        </is>
+      </c>
+      <c r="B11" s="55" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="C11" s="54" t="inlineStr">
+        <is>
+          <t>아파트형 부유바닥 · 싱글레이어</t>
+        </is>
+      </c>
+      <c r="D11" s="55" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="E11" s="54" t="inlineStr">
+        <is>
+          <t>차음</t>
+        </is>
+      </c>
+      <c r="F11" s="55" t="inlineStr">
+        <is>
+          <t>아파트 전용</t>
+        </is>
+      </c>
+      <c r="G11" s="55" t="n"/>
+      <c r="H11" s="54" t="inlineStr">
+        <is>
+          <t>관악·성악·바이올린·업라이트 피아노</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="54" t="inlineStr">
+        <is>
+          <t>AC-F-M2</t>
+        </is>
+      </c>
+      <c r="B12" s="55" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="C12" s="54" t="inlineStr">
+        <is>
+          <t>아파트형 부유바닥 · 더블레이어</t>
+        </is>
+      </c>
+      <c r="D12" s="55" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="E12" s="54" t="inlineStr">
+        <is>
+          <t>차음 (2단 절연)</t>
+        </is>
+      </c>
+      <c r="F12" s="55" t="inlineStr">
+        <is>
+          <t>아파트 전용</t>
+        </is>
+      </c>
+      <c r="G12" s="55" t="n"/>
+      <c r="H12" s="54" t="inlineStr">
+        <is>
+          <t>첼로·그랜드피아노·전자드럼·야간 사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="37" t="inlineStr">
         <is>
           <t>절벽 구간</t>
         </is>
       </c>
-      <c r="B11" s="38" t="n"/>
-      <c r="C11" s="39" t="n"/>
-      <c r="D11" s="38" t="n"/>
-      <c r="E11" s="39" t="n"/>
-      <c r="F11" s="38" t="n"/>
-      <c r="G11" s="38" t="n"/>
-      <c r="H11" s="39" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="40" t="inlineStr">
+      <c r="B14" s="38" t="n"/>
+      <c r="C14" s="39" t="n"/>
+      <c r="D14" s="38" t="n"/>
+      <c r="E14" s="39" t="n"/>
+      <c r="F14" s="38" t="n"/>
+      <c r="G14" s="38" t="n"/>
+      <c r="H14" s="39" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="40" t="inlineStr">
         <is>
           <t>L1 → L0 : 공사 여부의 절벽 (견적이 몇 배 갈림)</t>
         </is>
       </c>
-      <c r="B12" s="38" t="n"/>
-      <c r="C12" s="39" t="n"/>
-      <c r="D12" s="38" t="n"/>
-      <c r="E12" s="39" t="n"/>
-      <c r="F12" s="38" t="n"/>
-      <c r="G12" s="38" t="n"/>
-      <c r="H12" s="39" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="41" t="inlineStr">
+      <c r="B15" s="38" t="n"/>
+      <c r="C15" s="39" t="n"/>
+      <c r="D15" s="38" t="n"/>
+      <c r="E15" s="39" t="n"/>
+      <c r="F15" s="38" t="n"/>
+      <c r="G15" s="38" t="n"/>
+      <c r="H15" s="39" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="41" t="inlineStr">
         <is>
           <t>L2 → L1 : 성능의 절벽 (차음 성립 여부가 갈림)</t>
-        </is>
-      </c>
-      <c r="B13" s="42" t="n"/>
-      <c r="C13" s="42" t="n"/>
-      <c r="D13" s="42" t="n"/>
-      <c r="E13" s="42" t="n"/>
-      <c r="F13" s="42" t="n"/>
-      <c r="G13" s="42" t="n"/>
-      <c r="H13" s="42" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="43" t="n"/>
-      <c r="B14" s="42" t="n"/>
-      <c r="C14" s="42" t="n"/>
-      <c r="D14" s="42" t="n"/>
-      <c r="E14" s="42" t="n"/>
-      <c r="F14" s="42" t="n"/>
-      <c r="G14" s="42" t="n"/>
-      <c r="H14" s="42" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="44" t="inlineStr">
-        <is>
-          <t>지하 · 습기 · 결로 우려 현장 (L2 · L3 공통 옵션)</t>
-        </is>
-      </c>
-      <c r="B15" s="42" t="n"/>
-      <c r="C15" s="42" t="n"/>
-      <c r="D15" s="42" t="n"/>
-      <c r="E15" s="42" t="n"/>
-      <c r="F15" s="42" t="n"/>
-      <c r="G15" s="42" t="n"/>
-      <c r="H15" s="42" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="45" t="inlineStr">
-        <is>
-          <t>· 슬래브 상부 아이소핑크(XPS) 20T 설치 — PE 방습필름 대체, 이음부 테이프 밀봉, 총 두께 +20mm</t>
         </is>
       </c>
       <c r="B16" s="42" t="n"/>
@@ -1090,11 +1216,7 @@
       <c r="H16" s="42" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="45" t="inlineStr">
-        <is>
-          <t>· XPS는 방진층이 아니라 하부 질량(슬래브의 연장)으로 취급. 방진 성능은 미네랄울이 담당</t>
-        </is>
-      </c>
+      <c r="A17" s="43" t="n"/>
       <c r="B17" s="42" t="n"/>
       <c r="C17" s="42" t="n"/>
       <c r="D17" s="42" t="n"/>
@@ -1104,9 +1226,9 @@
       <c r="H17" s="42" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="45" t="inlineStr">
-        <is>
-          <t>· 착공 전 함수율 확인 (1m×1m 비닐 밀봉 24~48시간, 결로 시 시공 보류)</t>
+      <c r="A18" s="44" t="inlineStr">
+        <is>
+          <t>지하 · 습기 · 결로 우려 현장 (L2 · L3 공통 옵션)</t>
         </is>
       </c>
       <c r="B18" s="42" t="n"/>
@@ -1120,7 +1242,7 @@
     <row r="19">
       <c r="A19" s="45" t="inlineStr">
         <is>
-          <t>· 불연 요구 현장은 준불연 XPS 적용</t>
+          <t>· 슬래브 상부 아이소핑크(XPS) 20T 설치 — PE 방습필름 대체, 이음부 테이프 밀봉, 총 두께 +20mm</t>
         </is>
       </c>
       <c r="B19" s="42" t="n"/>
@@ -1132,7 +1254,11 @@
       <c r="H19" s="42" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="42" t="n"/>
+      <c r="A20" s="45" t="inlineStr">
+        <is>
+          <t>· XPS는 방진층이 아니라 하부 질량(슬래브의 연장)으로 취급. 방진 성능은 미네랄울이 담당</t>
+        </is>
+      </c>
       <c r="B20" s="42" t="n"/>
       <c r="C20" s="42" t="n"/>
       <c r="D20" s="42" t="n"/>
@@ -1142,7 +1268,11 @@
       <c r="H20" s="42" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="42" t="n"/>
+      <c r="A21" s="45" t="inlineStr">
+        <is>
+          <t>· 착공 전 함수율 확인 (1m×1m 비닐 밀봉 24~48시간, 결로 시 시공 보류)</t>
+        </is>
+      </c>
       <c r="B21" s="42" t="n"/>
       <c r="C21" s="42" t="n"/>
       <c r="D21" s="42" t="n"/>
@@ -1150,6 +1280,1140 @@
       <c r="F21" s="42" t="n"/>
       <c r="G21" s="42" t="n"/>
       <c r="H21" s="42" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="45" t="inlineStr">
+        <is>
+          <t>· 불연 요구 현장은 준불연 XPS 적용</t>
+        </is>
+      </c>
+      <c r="B22" s="42" t="n"/>
+      <c r="C22" s="42" t="n"/>
+      <c r="D22" s="42" t="n"/>
+      <c r="E22" s="42" t="n"/>
+      <c r="F22" s="42" t="n"/>
+      <c r="G22" s="42" t="n"/>
+      <c r="H22" s="42" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="42" t="n"/>
+      <c r="B23" s="42" t="n"/>
+      <c r="C23" s="42" t="n"/>
+      <c r="D23" s="42" t="n"/>
+      <c r="E23" s="42" t="n"/>
+      <c r="F23" s="42" t="n"/>
+      <c r="G23" s="42" t="n"/>
+      <c r="H23" s="42" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="42" t="n"/>
+      <c r="B24" s="42" t="n"/>
+      <c r="C24" s="42" t="n"/>
+      <c r="D24" s="42" t="n"/>
+      <c r="E24" s="42" t="n"/>
+      <c r="F24" s="42" t="n"/>
+      <c r="G24" s="42" t="n"/>
+      <c r="H24" s="42" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>_템플릿</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>(등급명)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>(English subtitle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>메타</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="n"/>
+      <c r="C5" s="12" t="n"/>
+      <c r="D5" s="12" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>부위</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>등급</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>총 두께</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>분류</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>관련 도면</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>개정</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>사양</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n"/>
+      <c r="C13" s="12" t="n"/>
+      <c r="D13" s="12" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>명칭</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>총 두께</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>구성</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>하지</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>부착</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>층고 손실</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>하중</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>대응</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>비대응</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>적용</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>자재</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="n"/>
+      <c r="C25" s="12" t="n"/>
+      <c r="D25" s="12" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>규격</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="17" t="inlineStr"/>
+      <c r="B27" s="17" t="inlineStr"/>
+      <c r="C27" s="17" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="inlineStr"/>
+      <c r="B28" s="17" t="inlineStr"/>
+      <c r="C28" s="17" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="17" t="inlineStr"/>
+      <c r="B29" s="17" t="inlineStr"/>
+      <c r="C29" s="17" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="17" t="inlineStr"/>
+      <c r="B30" s="17" t="inlineStr"/>
+      <c r="C30" s="17" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="17" t="inlineStr"/>
+      <c r="B31" s="17" t="inlineStr"/>
+      <c r="C31" s="17" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="17" t="inlineStr"/>
+      <c r="B32" s="17" t="inlineStr"/>
+      <c r="C32" s="17" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>시공 순서</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="n"/>
+      <c r="C34" s="12" t="n"/>
+      <c r="D34" s="12" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>작업</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>확인사항</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B36" s="17" t="inlineStr"/>
+      <c r="C36" s="17" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B37" s="17" t="inlineStr"/>
+      <c r="C37" s="17" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B38" s="17" t="inlineStr"/>
+      <c r="C38" s="17" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="B39" s="17" t="inlineStr"/>
+      <c r="C39" s="17" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="B40" s="17" t="inlineStr"/>
+      <c r="C40" s="17" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="B41" s="17" t="inlineStr"/>
+      <c r="C41" s="17" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="B42" s="17" t="inlineStr"/>
+      <c r="C42" s="17" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="B43" s="17" t="inlineStr"/>
+      <c r="C43" s="17" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>시공상 유의사항</t>
+        </is>
+      </c>
+      <c r="B45" s="12" t="n"/>
+      <c r="C45" s="12" t="n"/>
+      <c r="D45" s="12" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="17" t="inlineStr"/>
+      <c r="B47" s="17" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="17" t="inlineStr"/>
+      <c r="B48" s="17" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="17" t="inlineStr"/>
+      <c r="B49" s="17" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="17" t="inlineStr"/>
+      <c r="B50" s="17" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="17" t="inlineStr"/>
+      <c r="B51" s="17" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="17" t="inlineStr"/>
+      <c r="B52" s="17" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>금지사항</t>
+        </is>
+      </c>
+      <c r="B54" s="12" t="n"/>
+      <c r="C54" s="12" t="n"/>
+      <c r="D54" s="12" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>금지</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>사유</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="19" t="inlineStr"/>
+      <c r="B56" s="19" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="19" t="inlineStr"/>
+      <c r="B57" s="19" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="19" t="inlineStr"/>
+      <c r="B58" s="19" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>도면번호 체계</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="21" t="inlineStr">
+        <is>
+          <t>AC - F - L0 - 01</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>접두어 - 부위 - 등급 - 세부</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="22" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>코드</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>접두어</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>Acoustic — 전 도면 공통</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>부위</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>바닥 Floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>부위</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>벽 Wall</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>부위</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>천장 Ceiling</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>부위</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>문 Door</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>부위</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>창 Glazing</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>부위</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>설비 Mechanical (덕트 · 환기)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>부위</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>접합부 Joint — 등급 무관 공통 상세</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>등급</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>L0~L5</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>성능 등급 (한 자리)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>세부</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>-01, -02</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>부분 상세 (필요 시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>J 시리즈 예시</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>AC-J-01</t>
+        </is>
+      </c>
+      <c r="B19" s="25" t="inlineStr">
+        <is>
+          <t>연변 이격 상세 (Perimeter isolation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>AC-J-02</t>
+        </is>
+      </c>
+      <c r="B20" s="25" t="inlineStr">
+        <is>
+          <t>문턱 · 출입구 접합</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>AC-J-03</t>
+        </is>
+      </c>
+      <c r="B21" s="25" t="inlineStr">
+        <is>
+          <t>관통부 방진 슬리브 (배관 · 전기)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>AC-J-04</t>
+        </is>
+      </c>
+      <c r="B22" s="25" t="inlineStr">
+        <is>
+          <t>벽 하부 접합 — 방식 A (벽 선시공)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>AC-J-05</t>
+        </is>
+      </c>
+      <c r="B23" s="25" t="inlineStr">
+        <is>
+          <t>벽 하부 접합 — 방식 B (박스 인 박스)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="62" t="inlineStr">
+        <is>
+          <t>도면 표기 규칙 (AC-00 참조)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="22" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>표기</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>질량판 공통</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>동일 색(연청색) + 재질별 무늬</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>합판 · 차음석고 · PB</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>합판</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>빗금 (45°)</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>목재 표기</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>차음석고보드</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>무늬 없음</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>질량판 기본형</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>PB (파티클보드)</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>점 패턴</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>파티클 표기</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>장선 · 목재 스터드</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>빗금 (색 구분)</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>질량판이 아닌 구조재</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="63" t="inlineStr">
+        <is>
+          <t>경량스터드 (강재)</t>
+        </is>
+      </c>
+      <c r="B32" s="63" t="inlineStr">
+        <is>
+          <t>교차 빗금</t>
+        </is>
+      </c>
+      <c r="C32" s="63" t="inlineStr">
+        <is>
+          <t>금속. 목재 단방향 빗금과 대비</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>돌차음판</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>진한 갈색 얇은 띠</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>그린글루와 동일 두께로 표기</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>그린글루</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>녹색 얇은 띠</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>제진층</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>방진층</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>연녹색 실선 박스</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>미네랄울 · 마블 · 슈퍼론 · 방진매트 공통. 밀도 차이는 라벨로 구분</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t>충진재</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>점선 박스</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="inlineStr">
+        <is>
+          <t>공동에 채운 흡음재</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="63" t="inlineStr">
+        <is>
+          <t>공기층</t>
+        </is>
+      </c>
+      <c r="B37" s="63" t="inlineStr">
+        <is>
+          <t>비움 (테두리 없음)</t>
+        </is>
+      </c>
+      <c r="C37" s="63" t="inlineStr">
+        <is>
+          <t>점선 박스(충진재)와 명확히 구분</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>아이소핑크 (XPS)</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>분홍 실선 박스</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="inlineStr">
+        <is>
+          <t>두께가 있으므로 실선. 옵션이어도 점선 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>PE 방습필름</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>갈색 점선</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>층으로 그릴 수 없는 두께</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>은박 EPE</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>청색 점선</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="inlineStr">
+        <is>
+          <t>M 시리즈. 필름과 색 구분</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="63" t="inlineStr">
+        <is>
+          <t>실란트</t>
+        </is>
+      </c>
+      <c r="B41" s="63" t="inlineStr">
+        <is>
+          <t>검정 삼각 비드</t>
+        </is>
+      </c>
+      <c r="C41" s="63" t="inlineStr">
+        <is>
+          <t>연변 이격부 · 관통부</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="63" t="inlineStr">
+        <is>
+          <t>레질리언트 채널</t>
+        </is>
+      </c>
+      <c r="B42" s="63" t="inlineStr">
+        <is>
+          <t>ㄷ자 · 열린 쪽이 구조체</t>
+        </is>
+      </c>
+      <c r="C42" s="63" t="inlineStr">
+        <is>
+          <t>플랜지가 구조체에 고정, 닫힌 면에 보드. 방향이 성능 좌우</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="63" t="inlineStr">
+        <is>
+          <t>방진행거</t>
+        </is>
+      </c>
+      <c r="B43" s="63" t="inlineStr">
+        <is>
+          <t>선 + 방진층 색 요소</t>
+        </is>
+      </c>
+      <c r="C43" s="63" t="inlineStr">
+        <is>
+          <t>별도 심볼 없음. 슬래브에서 내려오는 선 중간</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="14" t="inlineStr">
+        <is>
+          <t>마감재</t>
+        </is>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>층의 짧은 쪽(두께 방향)으로 분할선</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="inlineStr">
+        <is>
+          <t>바닥 · 벽 · 천장 공통. 도면 회전 시 선도 회전</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="14" t="inlineStr">
+        <is>
+          <t>구조 슬래브 · 구조벽</t>
+        </is>
+      </c>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>회색 민무늬</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="inlineStr">
+        <is>
+          <t>설계 대상이 아닌 조건이므로 무늬 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>원칙 1 — 색을 늘리지 않고 무늬로 재질을 구분한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>원칙 2 — 두께가 있으면 실선 박스, 없으면 점선.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>원칙 3 — 비어 있는 것(공기층)은 비워 둔다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>원칙 4 — 마감재 분할선은 층의 짧은 쪽으로 세운다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>원칙 5 — 방향이 성능을 좌우하는 부재는 형상으로 그린다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>※ 패턴 id는 한 페이지 내 유일해야 함. 부위+등급 코드를 접미사로 사용 (예: pw-w3, pm-c1)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1794,7 +3058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D86"/>
+  <dimension ref="A1:D87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1984,7 +3248,7 @@
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>돌차음판 자체 점착 + 상부 목공본드 + 타카 22mm</t>
+          <t>돌차음판 자체 점착 + 상부 목공본드 + 피스 3.9×25</t>
         </is>
       </c>
     </row>
@@ -2355,17 +3619,17 @@
     <row r="48">
       <c r="A48" s="17" t="inlineStr">
         <is>
-          <t>스테이플 타카핀</t>
+          <t>데크 피스</t>
         </is>
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>22mm (예비 19mm)</t>
+          <t>3.9 × 25mm</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>25mm 이상 반입 금지</t>
+          <t>32mm 이상 반입 금지. 타카 사용 금지</t>
         </is>
       </c>
     </row>
@@ -2780,60 +4044,72 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="19" t="inlineStr">
-        <is>
-          <t>슈퍼론 직접 보행 · 적재</t>
-        </is>
-      </c>
-      <c r="B82" s="19" t="inlineStr">
-        <is>
-          <t>국부 압착</t>
+      <c r="A82" s="53" t="inlineStr">
+        <is>
+          <t>스테이플 타카 사용</t>
+        </is>
+      </c>
+      <c r="B82" s="53" t="inlineStr">
+        <is>
+          <t>핀이 삐져나와 삐걱임 유발 — 바닥은 피스만</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="19" t="inlineStr">
         <is>
-          <t>연변 이격 생략</t>
+          <t>슈퍼론 직접 보행 · 적재</t>
         </is>
       </c>
       <c r="B83" s="19" t="inlineStr">
         <is>
-          <t>측면전달음 발생 — 제조사 지침과 별개</t>
+          <t>국부 압착</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="19" t="inlineStr">
         <is>
-          <t>슬래브 앵커 고정</t>
+          <t>연변 이격 생략</t>
         </is>
       </c>
       <c r="B84" s="19" t="inlineStr">
         <is>
-          <t>부유 구조 무효화</t>
+          <t>측면전달음 발생 — 제조사 지침과 별개</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="19" t="inlineStr">
         <is>
-          <t>경화형 퍼티 실란트</t>
+          <t>슬래브 앵커 고정</t>
         </is>
       </c>
       <c r="B85" s="19" t="inlineStr">
         <is>
-          <t>굳으면 강체 브릿지</t>
+          <t>부유 구조 무효화</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="19" t="inlineStr">
         <is>
+          <t>경화형 퍼티 실란트</t>
+        </is>
+      </c>
+      <c r="B86" s="19" t="inlineStr">
+        <is>
+          <t>굳으면 강체 브릿지</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="19" t="inlineStr">
+        <is>
           <t>저역 음원 현장 적용</t>
         </is>
       </c>
-      <c r="B86" s="19" t="inlineStr">
+      <c r="B87" s="19" t="inlineStr">
         <is>
           <t>드럼 · 앰프 · 서브우퍼는 L4 이상</t>
         </is>
@@ -2850,7 +4126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D107"/>
+  <dimension ref="A1:D108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3040,7 +4316,7 @@
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>돌차음판 자체 점착 + 목공본드 + 나사 38mm, 200~250mm 간격</t>
+          <t>돌차음판 자체 점착 + 목공본드 + 피스 3.9×38, 200~250mm 간격</t>
         </is>
       </c>
     </row>
@@ -3642,12 +4918,12 @@
     <row r="67">
       <c r="A67" s="17" t="inlineStr">
         <is>
-          <t>나사</t>
+          <t>피스</t>
         </is>
       </c>
       <c r="B67" s="17" t="inlineStr">
         <is>
-          <t>38mm (예비 32mm)</t>
+          <t>3.9 × 38mm</t>
         </is>
       </c>
       <c r="C67" s="17" t="inlineStr">
@@ -3890,7 +5166,7 @@
       </c>
       <c r="B84" s="17" t="inlineStr">
         <is>
-          <t>나사 체결</t>
+          <t>피스 체결</t>
         </is>
       </c>
       <c r="C84" s="17" t="inlineStr">
@@ -3954,12 +5230,12 @@
     <row r="90">
       <c r="A90" s="17" t="inlineStr">
         <is>
-          <t>나사 길이</t>
+          <t>피스 길이</t>
         </is>
       </c>
       <c r="B90" s="17" t="inlineStr">
         <is>
-          <t>38mm 표준, 예비 32mm. 현장에 38mm만 반입. 첫 10개 하부 합판 뒷면 확인</t>
+          <t>3.9×38. 현장에 38mm만 반입. 첫 10개 하부 합판 뒷면 확인</t>
         </is>
       </c>
     </row>
@@ -4072,7 +5348,7 @@
     <row r="101">
       <c r="A101" s="19" t="inlineStr">
         <is>
-          <t>41mm 이상 나사</t>
+          <t>50mm 이상 피스</t>
         </is>
       </c>
       <c r="B101" s="19" t="inlineStr">
@@ -4082,72 +5358,84 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="19" t="inlineStr">
-        <is>
-          <t>미네랄울 압축 시공</t>
-        </is>
-      </c>
-      <c r="B102" s="19" t="inlineStr">
-        <is>
-          <t>동적강성 급등 · 방진 성능 상실</t>
+      <c r="A102" s="53" t="inlineStr">
+        <is>
+          <t>스테이플 타카 사용</t>
+        </is>
+      </c>
+      <c r="B102" s="53" t="inlineStr">
+        <is>
+          <t>핀이 삐져나와 삐걱임 유발 — 바닥은 피스만</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="19" t="inlineStr">
         <is>
-          <t>미네랄울 직접 보행 · 적재</t>
+          <t>미네랄울 압축 시공</t>
         </is>
       </c>
       <c r="B103" s="19" t="inlineStr">
         <is>
-          <t>국부 압착</t>
+          <t>동적강성 급등 · 방진 성능 상실</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="19" t="inlineStr">
         <is>
-          <t>연변 이격 생략</t>
+          <t>미네랄울 직접 보행 · 적재</t>
         </is>
       </c>
       <c r="B104" s="19" t="inlineStr">
         <is>
-          <t>측면전달음 발생</t>
+          <t>국부 압착</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="19" t="inlineStr">
         <is>
-          <t>슬래브 앵커 고정</t>
+          <t>연변 이격 생략</t>
         </is>
       </c>
       <c r="B105" s="19" t="inlineStr">
         <is>
-          <t>부유 구조 무효화</t>
+          <t>측면전달음 발생</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="19" t="inlineStr">
         <is>
-          <t>중량물 직치</t>
+          <t>슬래브 앵커 고정</t>
         </is>
       </c>
       <c r="B106" s="19" t="inlineStr">
         <is>
-          <t>점하중 압착 — 하중분산판 필수</t>
+          <t>부유 구조 무효화</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="19" t="inlineStr">
         <is>
+          <t>중량물 직치</t>
+        </is>
+      </c>
+      <c r="B107" s="19" t="inlineStr">
+        <is>
+          <t>점하중 압착 — 하중분산판 필수</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="19" t="inlineStr">
+        <is>
           <t>저역 음원 현장 적용</t>
         </is>
       </c>
-      <c r="B107" s="19" t="inlineStr">
+      <c r="B108" s="19" t="inlineStr">
         <is>
           <t>드럼 · 앰프 · 서브우퍼는 L4 이상</t>
         </is>
@@ -4169,7 +5457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D125"/>
+  <dimension ref="A1:D126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4371,7 +5659,7 @@
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>돌차음판 자체 점착 + 목공본드 + 나사 50mm, 200mm 간격</t>
+          <t>돌차음판 자체 점착 + 목공본드 + 피스 3.9×50, 200mm 간격</t>
         </is>
       </c>
     </row>
@@ -4658,7 +5946,7 @@
     <row r="46">
       <c r="A46" s="29" t="inlineStr">
         <is>
-          <t>왜 석고 사이인가: 구속감쇠는 두 강체판 사이에서 전단변형이 일어나야 작동. 돌차음판은 무르고 자체 점착층이 있어 전단이 흡수되므로 제진 효과가 나오지 않음. 석고↔석고가 정통 배치이며 나사로 압착해야 층간 밀착 확보.</t>
+          <t>왜 석고 사이인가: 구속감쇠는 두 강체판 사이에서 전단변형이 일어나야 작동. 돌차음판은 무르고 자체 점착층이 있어 전단이 흡수되므로 제진 효과가 나오지 않음. 석고↔석고가 정통 배치이며 피스로 압착해야 층간 밀착 확보.</t>
         </is>
       </c>
     </row>
@@ -5076,12 +6364,12 @@
     <row r="80">
       <c r="A80" s="17" t="inlineStr">
         <is>
-          <t>나사</t>
+          <t>피스</t>
         </is>
       </c>
       <c r="B80" s="17" t="inlineStr">
         <is>
-          <t>50mm (예비 45mm)</t>
+          <t>3.9 × 50mm</t>
         </is>
       </c>
       <c r="C80" s="17" t="inlineStr">
@@ -5354,7 +6642,7 @@
       </c>
       <c r="B99" s="17" t="inlineStr">
         <is>
-          <t>나사 체결</t>
+          <t>피스 체결</t>
         </is>
       </c>
       <c r="C99" s="17" t="inlineStr">
@@ -5418,12 +6706,12 @@
     <row r="105">
       <c r="A105" s="17" t="inlineStr">
         <is>
-          <t>나사 길이</t>
+          <t>피스 길이</t>
         </is>
       </c>
       <c r="B105" s="17" t="inlineStr">
         <is>
-          <t>50mm 표준, 예비 45mm. 현장에 50mm만 반입. L2(38mm)와 혼입 금지 — 자재 분리 보관</t>
+          <t>3.9×50. 현장에 50mm만 반입. L2(38mm)와 혼입 금지 — 자재 분리 보관</t>
         </is>
       </c>
     </row>
@@ -5560,7 +6848,7 @@
     <row r="118">
       <c r="A118" s="19" t="inlineStr">
         <is>
-          <t>55mm 이상 나사</t>
+          <t>64mm 이상 피스</t>
         </is>
       </c>
       <c r="B118" s="19" t="inlineStr">
@@ -5606,48 +6894,60 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="19" t="inlineStr">
-        <is>
-          <t>미네랄울 압축 시공</t>
-        </is>
-      </c>
-      <c r="B122" s="19" t="inlineStr">
-        <is>
-          <t>동적강성 급등 · 방진 성능 상실</t>
+      <c r="A122" s="53" t="inlineStr">
+        <is>
+          <t>스테이플 타카 사용</t>
+        </is>
+      </c>
+      <c r="B122" s="53" t="inlineStr">
+        <is>
+          <t>핀이 삐져나와 삐걱임 유발 — 바닥은 피스만</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="19" t="inlineStr">
         <is>
-          <t>연변 이격 생략</t>
+          <t>미네랄울 압축 시공</t>
         </is>
       </c>
       <c r="B123" s="19" t="inlineStr">
         <is>
-          <t>측면전달음 발생</t>
+          <t>동적강성 급등 · 방진 성능 상실</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="19" t="inlineStr">
         <is>
-          <t>슬래브 앵커 고정</t>
+          <t>연변 이격 생략</t>
         </is>
       </c>
       <c r="B124" s="19" t="inlineStr">
         <is>
-          <t>부유 구조 무효화</t>
+          <t>측면전달음 발생</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="19" t="inlineStr">
         <is>
+          <t>슬래브 앵커 고정</t>
+        </is>
+      </c>
+      <c r="B125" s="19" t="inlineStr">
+        <is>
+          <t>부유 구조 무효화</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="19" t="inlineStr">
+        <is>
           <t>저역 음원 현장 적용</t>
         </is>
       </c>
-      <c r="B125" s="19" t="inlineStr">
+      <c r="B126" s="19" t="inlineStr">
         <is>
           <t>드럼 · 앰프 · 서브우퍼는 L4 이상</t>
         </is>
@@ -5671,7 +6971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D128"/>
+  <dimension ref="A1:D130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5701,7 +7001,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
@@ -5784,7 +7083,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -5827,7 +7125,7 @@
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>방진고무 25T + 투바이 각재 69T(충진 50T) + 합판 12T + 그린글루 + 합판 12T + 돌차음판 4T + 마감</t>
+          <t>방진고무 25T + 투바이 장선 28×67(충진 50T) + 합판 12T + 그린글루 + 합판 12T + 돌차음판 4T + 마감</t>
         </is>
       </c>
     </row>
@@ -5839,7 +7137,7 @@
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>십자형 탄성고무 25(T)×75×110 · 각재 하부 점지지</t>
+          <t>십자형 탄성고무 25(T)×75×110 · 장선 하부 점지지</t>
         </is>
       </c>
     </row>
@@ -5851,7 +7149,7 @@
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>투바이 각재 69T · 400mm 간격</t>
+          <t>투바이 장선 28×67 · 400mm 간격</t>
         </is>
       </c>
     </row>
@@ -5899,7 +7197,7 @@
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>목공본드 + 나사 32mm (합판→합판) / 각재 고정 나사 별도</t>
+          <t>목공본드 + 데크 피스 3.9×50 (데크→장선 관통) · 200mm 간격</t>
         </is>
       </c>
     </row>
@@ -5951,7 +7249,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28" ht="56" customHeight="1">
       <c r="A28" s="27" t="inlineStr">
         <is>
@@ -5959,15 +7256,13 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
     <row r="30" ht="56" customHeight="1">
       <c r="A30" s="33" t="inlineStr">
         <is>
-          <t>장선 공법은 습기에 강함 — 별도 방습 사양 불필요. 방진고무 무흡수, 각재가 슬래브에서 25mm 이격, 공동이 통풍 경로. L2·L3의 아이소핑크 방습층은 오히려 통풍을 막으므로 적용하지 않음. PE 방습필름은 각재 하부 목재·충진재 보호 목적으로 유지. 충진재가 무기섬유(24K)면 곰팡이 우려 → 습기 현장은 압축마블스펀지 선택.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31"/>
+          <t>장선 공법은 습기에 강함 — 별도 방습 사양 불필요. 방진고무 무흡수, 장선이 슬래브에서 25mm 이격, 공동이 통풍 경로. L2·L3의 아이소핑크 방습층은 오히려 통풍을 막으므로 적용하지 않음. PE 방습필름은 장선 하부 목재·충진재 보호 목적으로 유지. 충진재가 무기섬유(24K)면 곰팡이 우려 → 습기 현장은 압축마블스펀지 선택.</t>
+        </is>
+      </c>
+    </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
@@ -6080,7 +7375,6 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
     <row r="40" ht="56" customHeight="1">
       <c r="A40" s="27" t="inlineStr">
         <is>
@@ -6088,15 +7382,13 @@
         </is>
       </c>
     </row>
-    <row r="41"/>
     <row r="42" ht="56" customHeight="1">
       <c r="A42" s="48" t="inlineStr">
         <is>
-          <t>차음석고보드를 데크에 넣지 않음: 각재 400 간격을 데크가 스팬으로 건너가 보행 시 반복 굽힘 발생. 석고는 취성 재료로 균열·분화되며 마감 아래라 발견이 늦음. 질량 보강은 상부 합판 15T 상향(L5 방식).</t>
-        </is>
-      </c>
-    </row>
-    <row r="43"/>
+          <t>차음석고보드를 데크에 넣지 않음: 장선 400 간격을 데크가 스팬으로 건너가 보행 시 반복 굽힘 발생. 석고는 취성 재료로 균열·분화되며 마감 아래라 발견이 늦음. 질량 보강은 상부 합판 15T 상향(L5 방식).</t>
+        </is>
+      </c>
+    </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
         <is>
@@ -6151,7 +7443,7 @@
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>각재 하부 · 400mm 간격 (㎡당 약 6.25개)</t>
+          <t>장선 하부 · 400mm 간격 (㎡당 약 6.25개)</t>
         </is>
       </c>
     </row>
@@ -6203,7 +7495,6 @@
         </is>
       </c>
     </row>
-    <row r="53"/>
     <row r="54" ht="56" customHeight="1">
       <c r="A54" s="29" t="inlineStr">
         <is>
@@ -6211,7 +7502,6 @@
         </is>
       </c>
     </row>
-    <row r="55"/>
     <row r="56" ht="56" customHeight="1">
       <c r="A56" s="48" t="inlineStr">
         <is>
@@ -6219,7 +7509,6 @@
         </is>
       </c>
     </row>
-    <row r="57"/>
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
         <is>
@@ -6349,7 +7638,6 @@
         </is>
       </c>
     </row>
-    <row r="66"/>
     <row r="67" ht="56" customHeight="1">
       <c r="A67" s="27" t="inlineStr">
         <is>
@@ -6357,7 +7645,6 @@
         </is>
       </c>
     </row>
-    <row r="68"/>
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
         <is>
@@ -6398,19 +7685,19 @@
       </c>
       <c r="C71" s="17" t="inlineStr">
         <is>
-          <t>각재 하부 · 400 간격</t>
+          <t>장선 하부 · 400 간격</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="17" t="inlineStr">
         <is>
-          <t>투바이 각재</t>
+          <t>투바이 장선 (국산 각재)</t>
         </is>
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>69T</t>
+          <t>28×67</t>
         </is>
       </c>
       <c r="C72" s="17" t="inlineStr">
@@ -6524,12 +7811,12 @@
     <row r="79">
       <c r="A79" s="17" t="inlineStr">
         <is>
-          <t>나사</t>
+          <t>피스</t>
         </is>
       </c>
       <c r="B79" s="17" t="inlineStr">
         <is>
-          <t>32mm (합판→합판)</t>
+          <t>3.9 × 50mm (데크→장선)</t>
         </is>
       </c>
       <c r="C79" s="17" t="inlineStr">
@@ -6594,7 +7881,6 @@
         </is>
       </c>
     </row>
-    <row r="84"/>
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
         <is>
@@ -6678,7 +7964,7 @@
       </c>
       <c r="C90" s="17" t="inlineStr">
         <is>
-          <t>겹침 100mm · 각재 하부 목재 보호</t>
+          <t>겹침 100mm · 장선 하부 목재 보호</t>
         </is>
       </c>
     </row>
@@ -6693,7 +7979,7 @@
       </c>
       <c r="C91" s="17" t="inlineStr">
         <is>
-          <t>각재 400 간격 · 패드 위치 표시</t>
+          <t>장선 400 간격 · 패드 위치 표시</t>
         </is>
       </c>
     </row>
@@ -6718,7 +8004,7 @@
       </c>
       <c r="B93" s="17" t="inlineStr">
         <is>
-          <t>각재 설치</t>
+          <t>장선 설치</t>
         </is>
       </c>
       <c r="C93" s="17" t="inlineStr">
@@ -6738,7 +8024,7 @@
       </c>
       <c r="C94" s="17" t="inlineStr">
         <is>
-          <t>각재 끝단 벽에서 10mm 이격 (AC-J-01)</t>
+          <t>장선 끝단 벽에서 10mm 이격 (AC-J-01)</t>
         </is>
       </c>
     </row>
@@ -6753,7 +8039,7 @@
       </c>
       <c r="C95" s="17" t="inlineStr">
         <is>
-          <t>압축하지 않고 채움 · 각재 높이 이내</t>
+          <t>압축하지 않고 채움 · 장선 높이 이내</t>
         </is>
       </c>
     </row>
@@ -6768,7 +8054,7 @@
       </c>
       <c r="C96" s="17" t="inlineStr">
         <is>
-          <t>이음선 각재 위에 · 엇갈림 배치</t>
+          <t>이음선 장선 위에 · 엇갈림 배치</t>
         </is>
       </c>
     </row>
@@ -6798,7 +8084,7 @@
       </c>
       <c r="C98" s="17" t="inlineStr">
         <is>
-          <t>하부와 직각 방향 · 나사 32mm 즉시 압착</t>
+          <t>하부와 직각 방향 · 피스 32mm 즉시 압착</t>
         </is>
       </c>
     </row>
@@ -6847,7 +8133,6 @@
         </is>
       </c>
     </row>
-    <row r="102"/>
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
         <is>
@@ -6878,268 +8163,291 @@
       </c>
       <c r="B105" s="17" t="inlineStr">
         <is>
-          <t>L4 최대 실패 요인. 각재를 앵커로 고정하면 강체 브릿지 — 각재는 방진고무 위에 얹혀만 있어야 함</t>
+          <t>L4 최대 실패 요인. 장선을 앵커로 고정하면 강체 브릿지 — 장선은 방진고무 위에 얹혀만 있어야 함</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="17" t="inlineStr">
-        <is>
-          <t>레벨 조정은 패드로</t>
-        </is>
-      </c>
-      <c r="B106" s="17" t="inlineStr">
-        <is>
-          <t>슬래브 구배 시 패드 하부에 동일 재질 심 사용. 목재 쐐기·모르타르 금지</t>
+      <c r="A106" s="14" t="inlineStr">
+        <is>
+          <t>공동 깊이는 장선 규격으로</t>
+        </is>
+      </c>
+      <c r="B106" s="14" t="inlineStr">
+        <is>
+          <t>배선 공간·공동 확대가 필요하면 장선을 투바이포·투바이식스 구조재로 상향. 장선 하부에 나무 블록·스페이서를 끼우면 패드 중앙에만 하중이 집중되어 편심 압착·좌굴·접합부 이완 발생. 준공 1~3년 후 침하·삐걱임으로 나타나 원인 규명이 어려움</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="17" t="inlineStr">
         <is>
-          <t>패드 방향</t>
+          <t>레벨 조정은 패드로</t>
         </is>
       </c>
       <c r="B107" s="17" t="inlineStr">
         <is>
-          <t>긴 변(110)을 각재와 직각 배치 — 각재 폭 방향 하중 분산</t>
+          <t>슬래브 구배 시 패드 하부에 동일 재질 심 사용. 목재 쐐기·모르타르 금지</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="17" t="inlineStr">
         <is>
-          <t>충진재 압축 금지</t>
+          <t>패드 방향</t>
         </is>
       </c>
       <c r="B108" s="17" t="inlineStr">
         <is>
-          <t>각재 높이(69mm) 이내에서 자연스럽게 채움. 눌러 넣으면 각재 부상</t>
+          <t>긴 변(110)을 각재와 직각 배치 — 각재 폭 방향 하중 분산</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="17" t="inlineStr">
         <is>
-          <t>합판 이음선</t>
+          <t>충진재 압축 금지</t>
         </is>
       </c>
       <c r="B109" s="17" t="inlineStr">
         <is>
-          <t>하부 이음선은 각재 위에. 상부는 하부와 직각 방향으로 포설</t>
+          <t>장선 높이(69mm) 이내에서 자연스럽게 채움. 눌러 넣으면 장선 부상</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="17" t="inlineStr">
         <is>
-          <t>그린글루 시간 관리</t>
+          <t>합판 이음선</t>
         </is>
       </c>
       <c r="B110" s="17" t="inlineStr">
         <is>
-          <t>도포 후 15분 내 압착. 3~4㎡ 구간 분할. 완전 성능 약 30일 후</t>
+          <t>하부 이음선은 장선 위에. 상부는 하부와 직각 방향으로 포설</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="17" t="inlineStr">
         <is>
-          <t>나사 길이</t>
+          <t>그린글루 시간 관리</t>
         </is>
       </c>
       <c r="B111" s="17" t="inlineStr">
         <is>
-          <t>합판 2겹 32mm. 각재 관통해 패드·슬래브에 닿지 않게</t>
+          <t>도포 후 15분 내 압착. 3~4㎡ 구간 분할. 완전 성능 약 30일 후</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="17" t="inlineStr">
         <is>
-          <t>연변 이격</t>
+          <t>피스 길이</t>
         </is>
       </c>
       <c r="B112" s="17" t="inlineStr">
         <is>
-          <t>각재 끝단·데크 전체가 벽·기둥·문틀 비접촉. 걸레받이는 데크에만 고정</t>
+          <t>합판 2겹 32mm. 장선 관통해 패드·슬래브에 닿지 않게</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="17" t="inlineStr">
         <is>
-          <t>중량물 구역</t>
+          <t>연변 이격</t>
         </is>
       </c>
       <c r="B113" s="17" t="inlineStr">
         <is>
-          <t>드럼 라이저·앰프 스택 위치는 각재 간격 300mm로 축소 또는 패드 추가</t>
+          <t>장선 끝단·데크 전체가 벽·기둥·문틀 비접촉. 걸레받이는 데크에만 고정</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="17" t="inlineStr">
         <is>
-          <t>VOC · 냄새</t>
+          <t>중량물 구역</t>
         </is>
       </c>
       <c r="B114" s="17" t="inlineStr">
         <is>
-          <t>고무칩+우레탄 제품은 밀폐·난방 공간에서 냄새 발생 가능. 환기 기간 확보, 온돌 병용 시 사전 고지</t>
+          <t>드럼 라이저·앰프 스택 위치는 장선 간격 300mm로 축소 또는 패드 추가</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="17" t="inlineStr">
         <is>
+          <t>VOC · 냄새</t>
+        </is>
+      </c>
+      <c r="B115" s="17" t="inlineStr">
+        <is>
+          <t>고무칩+우레탄 제품은 밀폐·난방 공간에서 냄새 발생 가능. 환기 기간 확보, 온돌 병용 시 사전 고지</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="17" t="inlineStr">
+        <is>
           <t>관통부</t>
         </is>
       </c>
-      <c r="B115" s="17" t="inlineStr">
+      <c r="B116" s="17" t="inlineStr">
         <is>
           <t>배관·전기 관통 시 방진 슬리브 + 실란트</t>
         </is>
       </c>
     </row>
-    <row r="116"/>
-    <row r="117">
-      <c r="A117" s="11" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="11" t="inlineStr">
         <is>
           <t>금지사항</t>
         </is>
       </c>
-      <c r="B117" s="12" t="n"/>
-      <c r="C117" s="12" t="n"/>
-      <c r="D117" s="12" t="n"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="3" t="inlineStr">
+      <c r="B118" s="12" t="n"/>
+      <c r="C118" s="12" t="n"/>
+      <c r="D118" s="12" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
         <is>
           <t>금지</t>
         </is>
       </c>
-      <c r="B118" s="3" t="inlineStr">
+      <c r="B119" s="3" t="inlineStr">
         <is>
           <t>사유</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="19" t="inlineStr">
-        <is>
-          <t>각재 슬래브 앵커 고정</t>
-        </is>
-      </c>
-      <c r="B119" s="19" t="inlineStr">
-        <is>
-          <t>강체 브릿지 — 전 시스템 무효화</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="19" t="inlineStr">
         <is>
-          <t>목재 쐐기 · 모르타르 레벨링</t>
+          <t>각재 슬래브 앵커 고정</t>
         </is>
       </c>
       <c r="B120" s="19" t="inlineStr">
         <is>
-          <t>브릿지 형성 — 동일 재질 심 사용</t>
+          <t>강체 브릿지 — 전 시스템 무효화</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="19" t="inlineStr">
         <is>
-          <t>방진고무 시트 재단 대체</t>
+          <t>목재 쐐기 · 모르타르 레벨링</t>
         </is>
       </c>
       <c r="B121" s="19" t="inlineStr">
         <is>
-          <t>형상계수 상실 — 십자형 전용품 사용</t>
+          <t>브릿지 형성 — 동일 재질 심 사용</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="19" t="inlineStr">
-        <is>
-          <t>데크에 차음석고보드 삽입</t>
-        </is>
-      </c>
-      <c r="B122" s="19" t="inlineStr">
-        <is>
-          <t>스팬 굽힘으로 균열 · 분화</t>
+      <c r="A122" s="53" t="inlineStr">
+        <is>
+          <t>장선 하부 블록 · 스페이서 삽입</t>
+        </is>
+      </c>
+      <c r="B122" s="53" t="inlineStr">
+        <is>
+          <t>하중 집중 · 좌굴 · 이완 — 공동 깊이는 장선 규격으로 확보</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="19" t="inlineStr">
         <is>
-          <t>충진재 압축 충전</t>
+          <t>방진고무 시트 재단 대체</t>
         </is>
       </c>
       <c r="B123" s="19" t="inlineStr">
         <is>
-          <t>각재 부상 · 데크 들뜸</t>
+          <t>형상계수 상실 — 십자형 전용품 사용</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="19" t="inlineStr">
         <is>
-          <t>각재 관통 나사</t>
+          <t>데크에 차음석고보드 삽입</t>
         </is>
       </c>
       <c r="B124" s="19" t="inlineStr">
         <is>
-          <t>패드 · 슬래브 접촉 시 브릿지</t>
+          <t>스팬 굽힘으로 균열 · 분화</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="19" t="inlineStr">
         <is>
-          <t>연변 이격 생략</t>
+          <t>충진재 압축 충전</t>
         </is>
       </c>
       <c r="B125" s="19" t="inlineStr">
         <is>
-          <t>측면전달음 발생</t>
+          <t>장선 부상 · 데크 들뜸</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="19" t="inlineStr">
         <is>
-          <t>패드 간격을 등급 변수로 사용</t>
+          <t>장선 관통 피스</t>
         </is>
       </c>
       <c r="B126" s="19" t="inlineStr">
         <is>
-          <t>침하 · 장기 크리프 위험</t>
+          <t>패드 · 슬래브 접촉 시 브릿지</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="53" t="inlineStr">
-        <is>
-          <t>아이소핑크 방습층 적용</t>
-        </is>
-      </c>
-      <c r="B127" s="53" t="inlineStr">
-        <is>
-          <t>공동 통풍 차단 — 장선 공법에는 불필요</t>
+      <c r="A127" s="19" t="inlineStr">
+        <is>
+          <t>연변 이격 생략</t>
+        </is>
+      </c>
+      <c r="B127" s="19" t="inlineStr">
+        <is>
+          <t>측면전달음 발생</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="19" t="inlineStr">
         <is>
+          <t>패드 간격을 등급 변수로 사용</t>
+        </is>
+      </c>
+      <c r="B128" s="19" t="inlineStr">
+        <is>
+          <t>침하 · 장기 크리프 위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="53" t="inlineStr">
+        <is>
+          <t>아이소핑크 방습층 적용</t>
+        </is>
+      </c>
+      <c r="B129" s="53" t="inlineStr">
+        <is>
+          <t>공동 통풍 차단 — 장선 공법에는 불필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="19" t="inlineStr">
+        <is>
           <t>추정 f0 대외 기재</t>
         </is>
       </c>
-      <c r="B128" s="19" t="inlineStr">
+      <c r="B130" s="19" t="inlineStr">
         <is>
           <t>제조사 처짐 데이터 미확보</t>
         </is>
@@ -7165,7 +8473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D135"/>
+  <dimension ref="A1:D137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -7195,7 +8503,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
@@ -7278,7 +8585,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -7319,12 +8625,12 @@
       </c>
       <c r="B15" s="50" t="inlineStr">
         <is>
-          <t>69T</t>
+          <t>28×67</t>
         </is>
       </c>
       <c r="C15" s="50" t="inlineStr">
         <is>
-          <t>89T</t>
+          <t>38×89</t>
         </is>
       </c>
       <c r="D15" s="50" t="inlineStr">
@@ -7399,7 +8705,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="48" t="inlineStr">
         <is>
@@ -7407,7 +8712,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
@@ -7450,7 +8754,7 @@
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>방진고무 25T + 투바이포 각재 89T(락울 50K 충진) + 합판 12T + 그린글루 + 합판 15T + 돌차음판 4T + 마감</t>
+          <t>방진고무 25T + 투바이포 장선 38×89(락울 50K 충진) + 합판 12T + 그린글루 + 합판 15T + 돌차음판 4T + 마감</t>
         </is>
       </c>
     </row>
@@ -7462,7 +8766,7 @@
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>십자형 탄성고무 25(T)×75×110 · 각재 하부 점지지</t>
+          <t>십자형 탄성고무 25(T)×75×110 · 장선 하부 점지지</t>
         </is>
       </c>
     </row>
@@ -7474,7 +8778,7 @@
       </c>
       <c r="B27" s="52" t="inlineStr">
         <is>
-          <t>투바이포 각재 89T · 400mm 간격</t>
+          <t>투바이포 장선 38×89 · 400mm 간격</t>
         </is>
       </c>
     </row>
@@ -7522,7 +8826,7 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>목공본드 + 나사 35mm (합판→합판) / 각재 고정 나사 별도</t>
+          <t>목공본드 + 데크 피스 4.8×64 (데크→장선 관통) · 200mm 간격</t>
         </is>
       </c>
     </row>
@@ -7574,7 +8878,6 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
@@ -7687,23 +8990,20 @@
         </is>
       </c>
     </row>
-    <row r="44"/>
     <row r="45" ht="58" customHeight="1">
       <c r="A45" s="27" t="inlineStr">
         <is>
-          <t>질량 상향폭은 크지 않으나 강성이 중요: L4(26) 대비 약 2 kg/㎡ 증가에 그치나, 상부 합판 15T는 굽힘강성이 두께의 3제곱에 비례하므로 12T 대비 약 1.95배. 각재 400 간격을 건너는 스팬 구조에서 처짐이 줄고 드럼 라이저·앰프 스택 점하중 분산이 개선됨. 차음보다 구조 성능을 위한 상향.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46"/>
+          <t>질량 상향폭은 크지 않으나 강성이 중요: L4(26) 대비 약 2 kg/㎡ 증가에 그치나, 상부 합판 15T는 굽힘강성이 두께의 3제곱에 비례하므로 12T 대비 약 1.95배. 장선 400 간격을 건너는 스팬 구조에서 처짐이 줄고 드럼 라이저·앰프 스택 점하중 분산이 개선됨. 차음보다 구조 성능을 위한 상향.</t>
+        </is>
+      </c>
+    </row>
     <row r="47" ht="58" customHeight="1">
       <c r="A47" s="48" t="inlineStr">
         <is>
-          <t>차음석고보드는 여전히 넣지 않음: 89T 각재로 공동이 깊어져도 데크가 스팬을 거는 조건은 동일. 석고는 반복 굽힘에서 균열·분화되므로 질량·강성 보강은 합판 두께 상향으로 처리.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48"/>
+          <t>차음석고보드는 여전히 넣지 않음: 투바이포로 공동이 깊어져도 데크가 스팬을 거는 조건은 동일. 석고는 반복 굽힘에서 균열·분화되므로 질량·강성 보강은 합판 두께 상향으로 처리.</t>
+        </is>
+      </c>
+    </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
         <is>
@@ -7746,7 +9046,7 @@
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>각재 하부 · 400mm 간격 (㎡당 약 6.25개)</t>
+          <t>장선 하부 · 400mm 간격 (㎡당 약 6.25개)</t>
         </is>
       </c>
     </row>
@@ -7794,11 +9094,10 @@
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>드럼 라이저 위치 각재 간격 300mm로 축소</t>
-        </is>
-      </c>
-    </row>
-    <row r="57"/>
+          <t>드럼 라이저 위치 장선 간격 300mm로 축소</t>
+        </is>
+      </c>
+    </row>
     <row r="58" ht="58" customHeight="1">
       <c r="A58" s="48" t="inlineStr">
         <is>
@@ -7806,7 +9105,6 @@
         </is>
       </c>
     </row>
-    <row r="59"/>
     <row r="60">
       <c r="A60" s="11" t="inlineStr">
         <is>
@@ -7864,7 +9162,7 @@
       </c>
       <c r="C63" s="17" t="inlineStr">
         <is>
-          <t>89T 각재 · 락울 50K</t>
+          <t>38×89 장선 · 락울 50K</t>
         </is>
       </c>
     </row>
@@ -7949,19 +9247,17 @@
       </c>
       <c r="C68" s="28" t="inlineStr">
         <is>
-          <t>벽 라인 각재 · 패드 보강 필수</t>
-        </is>
-      </c>
-    </row>
-    <row r="69"/>
+          <t>벽 라인 장선 · 패드 보강 필수</t>
+        </is>
+      </c>
+    </row>
     <row r="70" ht="58" customHeight="1">
       <c r="A70" s="27" t="inlineStr">
         <is>
-          <t>방식 B의 벽 하중: 경량스터드 + 석고 2겹 양면 · 층고 2.7m 기준 약 135 kg/m. 벽 하부 폭 150mm 환산 시 약 9 kPa로 면하중의 2.5배. 벽 라인은 각재 간격 200mm로 축소하고 패드 추가, 깔판(sole plate) 폭 300mm로 면압 분산. 천장까지 벽에 얹는 완전 박스인박스는 하중이 더 커지므로 별도 검토.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71"/>
+          <t>방식 B의 벽 하중: 경량스터드 + 석고 2겹 양면 · 층고 2.7m 기준 약 135 kg/m. 벽 하부 폭 150mm 환산 시 약 9 kPa로 면하중의 2.5배. 벽 라인은 장선 간격 200mm로 축소하고 패드 추가, 깔판(sole plate) 폭 300mm로 면압 분산. 천장까지 벽에 얹는 완전 박스인박스는 하중이 더 커지므로 별도 검토.</t>
+        </is>
+      </c>
+    </row>
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
         <is>
@@ -8002,19 +9298,19 @@
       </c>
       <c r="C74" s="17" t="inlineStr">
         <is>
-          <t>각재 하부 · 400 간격</t>
+          <t>장선 하부 · 400 간격</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="50" t="inlineStr">
         <is>
-          <t>투바이포 각재</t>
+          <t>투바이포 장선 (구조재)</t>
         </is>
       </c>
       <c r="B75" s="50" t="inlineStr">
         <is>
-          <t>89T</t>
+          <t>38×89</t>
         </is>
       </c>
       <c r="C75" s="50" t="inlineStr">
@@ -8128,12 +9424,12 @@
     <row r="82">
       <c r="A82" s="17" t="inlineStr">
         <is>
-          <t>나사</t>
+          <t>피스</t>
         </is>
       </c>
       <c r="B82" s="17" t="inlineStr">
         <is>
-          <t>35mm (합판→합판)</t>
+          <t>4.8 × 64mm (데크→장선)</t>
         </is>
       </c>
       <c r="C82" s="17" t="inlineStr">
@@ -8198,7 +9494,6 @@
         </is>
       </c>
     </row>
-    <row r="87"/>
     <row r="88" ht="58" customHeight="1">
       <c r="A88" s="29" t="inlineStr">
         <is>
@@ -8206,7 +9501,6 @@
         </is>
       </c>
     </row>
-    <row r="89"/>
     <row r="90">
       <c r="A90" s="11" t="inlineStr">
         <is>
@@ -8275,7 +9569,7 @@
       </c>
       <c r="C94" s="17" t="inlineStr">
         <is>
-          <t>겹침 100mm · 각재 하부 목재 보호</t>
+          <t>겹침 100mm · 장선 하부 목재 보호</t>
         </is>
       </c>
     </row>
@@ -8290,7 +9584,7 @@
       </c>
       <c r="C95" s="17" t="inlineStr">
         <is>
-          <t>각재 400 간격 · 벽 라인 200 간격 표시</t>
+          <t>장선 400 간격 · 벽 라인 200 간격 표시</t>
         </is>
       </c>
     </row>
@@ -8315,7 +9609,7 @@
       </c>
       <c r="B97" s="17" t="inlineStr">
         <is>
-          <t>각재 설치</t>
+          <t>장선 설치</t>
         </is>
       </c>
       <c r="C97" s="17" t="inlineStr">
@@ -8335,7 +9629,7 @@
       </c>
       <c r="C98" s="17" t="inlineStr">
         <is>
-          <t>방식 B 시 각재 · 패드 추가, 깔판 300mm</t>
+          <t>방식 B 시 장선 · 패드 추가, 깔판 300mm</t>
         </is>
       </c>
     </row>
@@ -8350,7 +9644,7 @@
       </c>
       <c r="C99" s="17" t="inlineStr">
         <is>
-          <t>각재 끝단 벽에서 10mm 이격 (AC-J-01)</t>
+          <t>장선 끝단 벽에서 10mm 이격 (AC-J-01)</t>
         </is>
       </c>
     </row>
@@ -8365,7 +9659,7 @@
       </c>
       <c r="C100" s="17" t="inlineStr">
         <is>
-          <t>압축하지 않고 채움 · 각재 높이 이내</t>
+          <t>압축하지 않고 채움 · 장선 높이 이내</t>
         </is>
       </c>
     </row>
@@ -8380,7 +9674,7 @@
       </c>
       <c r="C101" s="17" t="inlineStr">
         <is>
-          <t>이음선 각재 위에 · 엇갈림 배치</t>
+          <t>이음선 장선 위에 · 엇갈림 배치</t>
         </is>
       </c>
     </row>
@@ -8410,7 +9704,7 @@
       </c>
       <c r="C103" s="17" t="inlineStr">
         <is>
-          <t>하부와 직각 방향 · 나사 35mm 즉시 압착</t>
+          <t>하부와 직각 방향 · 피스 35mm 즉시 압착</t>
         </is>
       </c>
     </row>
@@ -8474,7 +9768,6 @@
         </is>
       </c>
     </row>
-    <row r="108"/>
     <row r="109">
       <c r="A109" s="11" t="inlineStr">
         <is>
@@ -8505,7 +9798,7 @@
       </c>
       <c r="B111" s="17" t="inlineStr">
         <is>
-          <t>각재를 앵커로 고정하면 강체 브릿지 — 방진고무 위에 얹혀만 있어야 함</t>
+          <t>장선을 앵커로 고정하면 강체 브릿지 — 방진고무 위에 얹혀만 있어야 함</t>
         </is>
       </c>
     </row>
@@ -8517,268 +9810,291 @@
       </c>
       <c r="B112" s="17" t="inlineStr">
         <is>
-          <t>방식 B 시 각재 간격 200mm로 축소, 패드 추가, 깔판 폭 300mm</t>
+          <t>방식 B 시 장선 간격 200mm로 축소, 패드 추가, 깔판 폭 300mm</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="17" t="inlineStr">
-        <is>
-          <t>레벨 조정은 패드로</t>
-        </is>
-      </c>
-      <c r="B113" s="17" t="inlineStr">
-        <is>
-          <t>슬래브 구배는 패드 하부 동일 재질 심으로. 목재 쐐기·모르타르 금지</t>
+      <c r="A113" s="14" t="inlineStr">
+        <is>
+          <t>공동 깊이는 장선 규격으로</t>
+        </is>
+      </c>
+      <c r="B113" s="14" t="inlineStr">
+        <is>
+          <t>배선 공간·공동 확대가 필요하면 장선을 투바이포·투바이식스 구조재로 상향. 장선 하부에 나무 블록·스페이서를 끼우면 패드 중앙에만 하중이 집중되어 편심 압착·좌굴·접합부 이완 발생. 준공 1~3년 후 침하·삐걱임으로 나타나 원인 규명이 어려움</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="17" t="inlineStr">
         <is>
-          <t>락울 압축 금지</t>
+          <t>레벨 조정은 패드로</t>
         </is>
       </c>
       <c r="B114" s="17" t="inlineStr">
         <is>
-          <t>각재 높이(89mm) 이내 자연 충전. 상부 39mm 공기층이 남는 것이 정상 — 추가 충진 금지</t>
+          <t>슬래브 구배는 패드 하부 동일 재질 심으로. 목재 쐐기·모르타르 금지</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="17" t="inlineStr">
         <is>
-          <t>합판 이음선</t>
+          <t>락울 압축 금지</t>
         </is>
       </c>
       <c r="B115" s="17" t="inlineStr">
         <is>
-          <t>하부 이음선은 각재 위에. 상부 15T는 하부와 직각 방향 포설</t>
+          <t>장선 높이(89mm) 이내 자연 충전. 상부 39mm 공기층이 남는 것이 정상 — 추가 충진 금지</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="17" t="inlineStr">
         <is>
-          <t>그린글루 시간 관리</t>
+          <t>합판 이음선</t>
         </is>
       </c>
       <c r="B116" s="17" t="inlineStr">
         <is>
-          <t>도포 후 15분 내 압착. 3~4㎡ 구간 분할. 완전 성능 약 30일 후 — 인수 시점 협의</t>
+          <t>하부 이음선은 장선 위에. 상부 15T는 하부와 직각 방향 포설</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="17" t="inlineStr">
         <is>
-          <t>나사 길이</t>
+          <t>그린글루 시간 관리</t>
         </is>
       </c>
       <c r="B117" s="17" t="inlineStr">
         <is>
-          <t>합판 2겹 35mm. 각재 관통해 패드·슬래브에 닿지 않게</t>
+          <t>도포 후 15분 내 압착. 3~4㎡ 구간 분할. 완전 성능 약 30일 후 — 인수 시점 협의</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="17" t="inlineStr">
         <is>
-          <t>드럼 라이저 구역</t>
+          <t>피스 길이</t>
         </is>
       </c>
       <c r="B118" s="17" t="inlineStr">
         <is>
-          <t>각재 간격 300mm 축소 + 데크 하부 각재 보강. 라이저 자체에도 별도 아이솔레이션</t>
+          <t>합판 2겹 35mm. 장선 관통해 패드·슬래브에 닿지 않게</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="17" t="inlineStr">
         <is>
-          <t>앰프 · 스피커</t>
+          <t>드럼 라이저 구역</t>
         </is>
       </c>
       <c r="B119" s="17" t="inlineStr">
         <is>
-          <t>바닥 직치 금지. 아이솔레이션 패드 또는 스탠드 병용</t>
+          <t>장선 간격 300mm 축소 + 데크 하부 각재 보강. 라이저 자체에도 별도 아이솔레이션</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="17" t="inlineStr">
         <is>
-          <t>연변 이격</t>
+          <t>앰프 · 스피커</t>
         </is>
       </c>
       <c r="B120" s="17" t="inlineStr">
         <is>
-          <t>각재 끝단·데크 전체 비접촉. 방식 B에서는 안쪽 벽이 바깥 겹과 이격</t>
+          <t>바닥 직치 금지. 아이솔레이션 패드 또는 스탠드 병용</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="17" t="inlineStr">
         <is>
-          <t>VOC · 냄새</t>
+          <t>연변 이격</t>
         </is>
       </c>
       <c r="B121" s="17" t="inlineStr">
         <is>
-          <t>고무칩+우레탄 제품은 밀폐·난방 공간에서 냄새 발생 가능. 환기 기간 확보</t>
+          <t>장선 끝단·데크 전체 비접촉. 방식 B에서는 안쪽 벽이 바깥 겹과 이격</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="17" t="inlineStr">
         <is>
+          <t>VOC · 냄새</t>
+        </is>
+      </c>
+      <c r="B122" s="17" t="inlineStr">
+        <is>
+          <t>고무칩+우레탄 제품은 밀폐·난방 공간에서 냄새 발생 가능. 환기 기간 확보</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="17" t="inlineStr">
+        <is>
           <t>관통부 · 설비</t>
         </is>
       </c>
-      <c r="B122" s="17" t="inlineStr">
+      <c r="B123" s="17" t="inlineStr">
         <is>
           <t>방진 슬리브 + 실란트. 합주실·녹음실은 공조 덕트 소음이 배경소음을 좌우 — 사일렌서·방진행거 별도 검토</t>
         </is>
       </c>
     </row>
-    <row r="123"/>
-    <row r="124">
-      <c r="A124" s="11" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="11" t="inlineStr">
         <is>
           <t>금지사항</t>
         </is>
       </c>
-      <c r="B124" s="12" t="n"/>
-      <c r="C124" s="12" t="n"/>
-      <c r="D124" s="12" t="n"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="3" t="inlineStr">
+      <c r="B125" s="12" t="n"/>
+      <c r="C125" s="12" t="n"/>
+      <c r="D125" s="12" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
         <is>
           <t>금지</t>
         </is>
       </c>
-      <c r="B125" s="3" t="inlineStr">
+      <c r="B126" s="3" t="inlineStr">
         <is>
           <t>사유</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="19" t="inlineStr">
-        <is>
-          <t>각재 슬래브 앵커 고정</t>
-        </is>
-      </c>
-      <c r="B126" s="19" t="inlineStr">
-        <is>
-          <t>강체 브릿지 — 전 시스템 무효화</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="19" t="inlineStr">
         <is>
-          <t>목재 쐐기 · 모르타르 레벨링</t>
+          <t>각재 슬래브 앵커 고정</t>
         </is>
       </c>
       <c r="B127" s="19" t="inlineStr">
         <is>
-          <t>브릿지 형성 — 동일 재질 심 사용</t>
+          <t>강체 브릿지 — 전 시스템 무효화</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="19" t="inlineStr">
         <is>
-          <t>방진고무 시트 재단 대체</t>
+          <t>목재 쐐기 · 모르타르 레벨링</t>
         </is>
       </c>
       <c r="B128" s="19" t="inlineStr">
         <is>
-          <t>형상계수 상실 — 십자형 전용품 사용</t>
+          <t>브릿지 형성 — 동일 재질 심 사용</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="19" t="inlineStr">
-        <is>
-          <t>데크에 차음석고보드 삽입</t>
-        </is>
-      </c>
-      <c r="B129" s="19" t="inlineStr">
-        <is>
-          <t>스팬 굽힘으로 균열 · 분화</t>
+      <c r="A129" s="53" t="inlineStr">
+        <is>
+          <t>장선 하부 블록 · 스페이서 삽입</t>
+        </is>
+      </c>
+      <c r="B129" s="53" t="inlineStr">
+        <is>
+          <t>하중 집중 · 좌굴 · 이완 — 공동 깊이는 장선 규격으로 확보</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="19" t="inlineStr">
         <is>
-          <t>벽 라인 보강 생략</t>
+          <t>방진고무 시트 재단 대체</t>
         </is>
       </c>
       <c r="B130" s="19" t="inlineStr">
         <is>
-          <t>선하중 집중 — 국부 압착 · 벽 기울음</t>
+          <t>형상계수 상실 — 십자형 전용품 사용</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="19" t="inlineStr">
         <is>
-          <t>락울 압축 충전</t>
+          <t>데크에 차음석고보드 삽입</t>
         </is>
       </c>
       <c r="B131" s="19" t="inlineStr">
         <is>
-          <t>각재 부상 · 데크 들뜸</t>
+          <t>스팬 굽힘으로 균열 · 분화</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="19" t="inlineStr">
         <is>
-          <t>가연성 충진재 사용</t>
+          <t>벽 라인 보강 생략</t>
         </is>
       </c>
       <c r="B132" s="19" t="inlineStr">
         <is>
-          <t>불연 요건 미충족 — L5 정의에 반함</t>
+          <t>선하중 집중 — 국부 압착 · 벽 기울음</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="19" t="inlineStr">
         <is>
-          <t>바닥 단독 시공</t>
+          <t>락울 압축 충전</t>
         </is>
       </c>
       <c r="B133" s="19" t="inlineStr">
         <is>
-          <t>벽 · 천장 미시공 시 저역 우회 — 투자 무효</t>
+          <t>장선 부상 · 데크 들뜸</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="53" t="inlineStr">
-        <is>
-          <t>아이소핑크 방습층 적용</t>
-        </is>
-      </c>
-      <c r="B134" s="53" t="inlineStr">
-        <is>
-          <t>공동 통풍 차단 — 장선 공법에는 불필요</t>
+      <c r="A134" s="19" t="inlineStr">
+        <is>
+          <t>가연성 충진재 사용</t>
+        </is>
+      </c>
+      <c r="B134" s="19" t="inlineStr">
+        <is>
+          <t>불연 요건 미충족 — L5 정의에 반함</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="19" t="inlineStr">
         <is>
+          <t>바닥 단독 시공</t>
+        </is>
+      </c>
+      <c r="B135" s="19" t="inlineStr">
+        <is>
+          <t>벽 · 천장 미시공 시 저역 우회 — 투자 무효</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="53" t="inlineStr">
+        <is>
+          <t>아이소핑크 방습층 적용</t>
+        </is>
+      </c>
+      <c r="B136" s="53" t="inlineStr">
+        <is>
+          <t>공동 통풍 차단 — 장선 공법에는 불필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="19" t="inlineStr">
+        <is>
           <t>추정 f0 대외 기재</t>
         </is>
       </c>
-      <c r="B135" s="19" t="inlineStr">
+      <c r="B137" s="19" t="inlineStr">
         <is>
           <t>제조사 처짐 데이터 미확보</t>
         </is>
@@ -8803,33 +10119,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>_템플릿</t>
+          <t>AC-F-M1</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>(등급명)</t>
+          <t>아파트형 부유바닥 · 싱글레이어</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>(English subtitle)</t>
+          <t>Residential floating floor / single resilient layer</t>
         </is>
       </c>
     </row>
@@ -8849,15 +10165,23 @@
           <t>부위</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr"/>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>바닥 Floor</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>등급</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr"/>
+          <t>유형</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
@@ -8865,23 +10189,35 @@
           <t>총 두께</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr"/>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>107 mm</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>분류</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr"/>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>차음</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>관련 도면</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="inlineStr"/>
+          <t>적용 현장</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>아파트 · 오피스텔</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
@@ -8911,7 +10247,11 @@
           <t>명칭</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr"/>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>아파트형 부유바닥 · 싱글레이어</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
@@ -8919,7 +10259,11 @@
           <t>총 두께</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr"/>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>107 mm</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
@@ -8927,39 +10271,59 @@
           <t>구성</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr"/>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>은박 EPE 3T + 마블 특마 50T + 합판 12T + PB 15T + 돌차음판 4T + PB 15T + 강화마루 8T</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>하지</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="inlineStr"/>
+          <t>방진층</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>마블충진재 특마 110K · 50T · 전면 부설</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>부착</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="inlineStr"/>
+          <t>라프트 면밀도</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>약 41 kg/㎡</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>층고 손실</t>
-        </is>
-      </c>
-      <c r="B19" s="14" t="inlineStr"/>
+          <t>체결</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>목공본드 + 피스 3.9×25 / 3.9×32 · 250~300mm 간격</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>하중</t>
-        </is>
-      </c>
-      <c r="B20" s="14" t="inlineStr"/>
+          <t>마감</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>강화마루 클릭 부동 시공 (언더레이 포함)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
@@ -8967,15 +10331,23 @@
           <t>대응</t>
         </is>
       </c>
-      <c r="B21" s="14" t="inlineStr"/>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>바이올린 · 비올라 · 성악 · 관악 · 업라이트 피아노 · 소출력 모니터</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="35" t="inlineStr">
         <is>
           <t>비대응</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr"/>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>어쿠스틱 드럼 · 서브우퍼 (M2 권장: 첼로·그랜드피아노·전자드럼·앰프·야간)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
@@ -8983,198 +10355,321 @@
           <t>적용</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>자재</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="n"/>
-      <c r="C25" s="12" t="n"/>
-      <c r="D25" s="12" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>아파트 · 오피스텔 (주거 건물 전용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="27" t="inlineStr">
+        <is>
+          <t>아파트 전용 사양: 장선 없는 전면 부설로 시공이 단순하고 분진이 거의 없어 거주 중 시공에 적합. 자재가 판재 형태(마블 420×1200)라 엘리베이터 반입 용이. 방진층에 재생폼을 쓰는 이유는 라프트 41 kg/㎡의 가벼운 조건에서 미네랄울(CS(10) 10kPa)이 거의 눌리지 않아 스프링으로 작동하지 못하기 때문. 이 하중대에서는 폼이 유리함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>라프트 면밀도 산출</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="n"/>
+      <c r="C27" s="12" t="n"/>
+      <c r="D27" s="12" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>층</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>두께</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>개략 면밀도</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>강화마루</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>8T</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="inlineStr">
+        <is>
+          <t>약 6.0</t>
+        </is>
+      </c>
+      <c r="D29" s="17" t="inlineStr">
+        <is>
+          <t>부동 시공</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>PB (상부)</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>15T</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="D30" s="17" t="inlineStr">
+        <is>
+          <t>벽 · 천장 공용</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t>돌차음판</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>4T</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="D31" s="17" t="inlineStr">
+        <is>
+          <t>질량 효율 최고</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="17" t="inlineStr">
+        <is>
+          <t>PB (중간)</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>15T</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="D32" s="17" t="inlineStr">
+        <is>
+          <t>벽 · 천장 공용</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="17" t="inlineStr">
+        <is>
+          <t>합판 (하부)</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>12T</t>
+        </is>
+      </c>
+      <c r="C33" s="17" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="D33" s="17" t="inlineStr">
+        <is>
+          <t>강성 · 습기 대응</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>54T</t>
+        </is>
+      </c>
+      <c r="C34" s="17" t="inlineStr">
+        <is>
+          <t>약 41 kg/㎡</t>
+        </is>
+      </c>
+      <c r="D34" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="27" t="inlineStr">
+        <is>
+          <t>판재 4장이 모두 다른 재료: 같은 재료를 여러 겹 쌓으면 임계주파수가 일치해 여러 층이 동시에 뚫림. 합판·PB·돌차음판 조합은 각 재료의 임계주파수가 달라 코인시던스 딥이 분산됨. 겹수를 늘리는 것보다 이종 조합이 실질적으로 중요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="27" t="inlineStr">
+        <is>
+          <t>하부만 합판인 이유: 마블 위 첫 판은 강성이 필요. PB는 합판 대비 굽힘강성 약 1/3이라 점하중 분산이 떨어지고, 습기에 취약해 마블과 접하는 면에 부적합. 상부 2장은 벽·천장 공용 PB로 통일하여 자재 종류를 줄임.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>방진층 · 은박 EPE</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="n"/>
+      <c r="C40" s="12" t="n"/>
+      <c r="D40" s="12" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="13" t="inlineStr">
+        <is>
+          <t>방진층 제품</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>마블충진재 특마 (재생 폴리우레탄 리본디드 폼)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>밀도</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>110 kg/㎥</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="13" t="inlineStr">
         <is>
           <t>규격</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="17" t="inlineStr"/>
-      <c r="B27" s="17" t="inlineStr"/>
-      <c r="C27" s="17" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="17" t="inlineStr"/>
-      <c r="B28" s="17" t="inlineStr"/>
-      <c r="C28" s="17" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="17" t="inlineStr"/>
-      <c r="B29" s="17" t="inlineStr"/>
-      <c r="C29" s="17" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="17" t="inlineStr"/>
-      <c r="B30" s="17" t="inlineStr"/>
-      <c r="C30" s="17" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="17" t="inlineStr"/>
-      <c r="B31" s="17" t="inlineStr"/>
-      <c r="C31" s="17" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="17" t="inlineStr"/>
-      <c r="B32" s="17" t="inlineStr"/>
-      <c r="C32" s="17" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="11" t="inlineStr">
-        <is>
-          <t>시공 순서</t>
-        </is>
-      </c>
-      <c r="B34" s="12" t="n"/>
-      <c r="C34" s="12" t="n"/>
-      <c r="D34" s="12" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>작업</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>확인사항</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="B36" s="17" t="inlineStr"/>
-      <c r="C36" s="17" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="B37" s="17" t="inlineStr"/>
-      <c r="C37" s="17" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="B38" s="17" t="inlineStr"/>
-      <c r="C38" s="17" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="B39" s="17" t="inlineStr"/>
-      <c r="C39" s="17" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="B40" s="17" t="inlineStr"/>
-      <c r="C40" s="17" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="B41" s="17" t="inlineStr"/>
-      <c r="C41" s="17" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="18" t="n">
-        <v>7</v>
-      </c>
-      <c r="B42" s="17" t="inlineStr"/>
-      <c r="C42" s="17" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="B43" s="17" t="inlineStr"/>
-      <c r="C43" s="17" t="inlineStr"/>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>420 × 1200mm · 50T</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="inlineStr">
+        <is>
+          <t>시공</t>
+        </is>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>전면 부설 · 밀착 맞댐 (압축 금지)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="11" t="inlineStr">
-        <is>
-          <t>시공상 유의사항</t>
-        </is>
-      </c>
-      <c r="B45" s="12" t="n"/>
-      <c r="C45" s="12" t="n"/>
-      <c r="D45" s="12" t="n"/>
+      <c r="A45" s="13" t="inlineStr">
+        <is>
+          <t>동탄성계수</t>
+        </is>
+      </c>
+      <c r="B45" s="49" t="inlineStr">
+        <is>
+          <t>데이터 미확보</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>내용</t>
+      <c r="A46" s="13" t="inlineStr">
+        <is>
+          <t>압축영구변형률</t>
+        </is>
+      </c>
+      <c r="B46" s="49" t="inlineStr">
+        <is>
+          <t>데이터 미확보</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="17" t="inlineStr"/>
-      <c r="B47" s="17" t="inlineStr"/>
+      <c r="A47" s="13" t="inlineStr">
+        <is>
+          <t>은박 EPE</t>
+        </is>
+      </c>
+      <c r="B47" s="14" t="inlineStr">
+        <is>
+          <t>3T · 슬래브 상부 전면</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="17" t="inlineStr"/>
-      <c r="B48" s="17" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="17" t="inlineStr"/>
-      <c r="B49" s="17" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="17" t="inlineStr"/>
-      <c r="B50" s="17" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="17" t="inlineStr"/>
-      <c r="B51" s="17" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="17" t="inlineStr"/>
-      <c r="B52" s="17" t="inlineStr"/>
+      <c r="A48" s="13" t="inlineStr">
+        <is>
+          <t>— 역할</t>
+        </is>
+      </c>
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>폼과 슬래브 직접 접촉 방지 · 방습 · 요철 흡수</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="58" customHeight="1">
+      <c r="A50" s="56" t="inlineStr">
+        <is>
+          <t>은박 EPE는 단열재가 아니라 완충층: 온돌 열을 차단하려는 것이 아니라 폼이 슬래브에 직접 닿지 않게 하는 것이 목적. 알루미늄 면이 복사열을 일부 반사해 접촉면의 급격한 온도 전달을 완화하며 방습·요철 흡수를 겸함. 두께 3mm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="58" customHeight="1">
+      <c r="A52" s="48" t="inlineStr">
+        <is>
+          <t>재생폼 데이터 미확보 — 선결 과제: 마블충진재의 동탄성계수·압축률·압축영구변형률 미확보. 재생 PU폼의 최대 약점은 장기 압축영구변형이며 무기섬유와 달리 회복되지 않음. 라프트 41 kg/㎡가 안전한지 판단하려면 하중 3~4kPa에서의 압축률과 압축영구변형률 필요. 확보 전까지 성능 수치를 대외 자료에 기재하지 않음.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t>금지사항</t>
+          <t>바닥난방 안내</t>
         </is>
       </c>
       <c r="B54" s="12" t="n"/>
@@ -9182,30 +10677,924 @@
       <c r="D54" s="12" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="A55" s="13" t="inlineStr">
+        <is>
+          <t>난방 효율</t>
+        </is>
+      </c>
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t>구조체 열저항이 커 온돌 난방이 실내에 거의 전달되지 않음</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="13" t="inlineStr">
+        <is>
+          <t>권장</t>
+        </is>
+      </c>
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t>해당 실은 냉난방 겸용 에어컨 등 별도 냉난방 계획</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="13" t="inlineStr">
+        <is>
+          <t>온돌 유지 시</t>
+        </is>
+      </c>
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t>저온 운전 권장. 은박 EPE로 폼 직접 접촉 방지</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="13" t="inlineStr">
+        <is>
+          <t>사전 협의</t>
+        </is>
+      </c>
+      <c r="B58" s="14" t="inlineStr">
+        <is>
+          <t>계약 단계에서 클라이언트에게 명확히 고지</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="58" customHeight="1">
+      <c r="A60" s="27" t="inlineStr">
+        <is>
+          <t>강제하지 않고 고지: 방음 구조체 위에서는 온돌 효율이 크게 떨어져 실사용에서 자연히 난방을 적게 쓰게 됨. 다만 고온 운전 시 슬래브 열이 폼에 전달되어 압축영구변형을 가속할 수 있으므로 저온 운전과 별도 냉난방을 권장. 밸브 차단을 시공 조건으로 요구하지 않음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>M1 · M2 선택 기준</t>
+        </is>
+      </c>
+      <c r="B62" s="12" t="n"/>
+      <c r="C62" s="12" t="n"/>
+      <c r="D62" s="12" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>조건</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="17" t="inlineStr">
+        <is>
+          <t>바이올린 · 비올라 · 관악 · 성악</t>
+        </is>
+      </c>
+      <c r="B64" s="18" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C64" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="17" t="inlineStr">
+        <is>
+          <t>업라이트 피아노</t>
+        </is>
+      </c>
+      <c r="B65" s="18" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C65" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="17" t="inlineStr">
+        <is>
+          <t>소출력 모니터 · 헤드폰 작업</t>
+        </is>
+      </c>
+      <c r="B66" s="18" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C66" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="17" t="inlineStr">
+        <is>
+          <t>첼로 · 콘트라베이스 (엔드핀 바닥 가진)</t>
+        </is>
+      </c>
+      <c r="B67" s="18" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="C67" s="18" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="17" t="inlineStr">
+        <is>
+          <t>그랜드피아노 (다리 하중 · 저역)</t>
+        </is>
+      </c>
+      <c r="B68" s="18" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="C68" s="18" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="17" t="inlineStr">
+        <is>
+          <t>전자드럼 (패드 타격)</t>
+        </is>
+      </c>
+      <c r="B69" s="18" t="inlineStr">
+        <is>
+          <t>✕</t>
+        </is>
+      </c>
+      <c r="C69" s="18" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="17" t="inlineStr">
+        <is>
+          <t>기타 · 베이스 앰프 (소출력)</t>
+        </is>
+      </c>
+      <c r="B70" s="18" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="C70" s="18" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="17" t="inlineStr">
+        <is>
+          <t>야간 사용 · 아래층 민감</t>
+        </is>
+      </c>
+      <c r="B71" s="18" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="C71" s="18" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="28" t="inlineStr">
+        <is>
+          <t>어쿠스틱 드럼 · 서브우퍼</t>
+        </is>
+      </c>
+      <c r="B72" s="61" t="inlineStr">
+        <is>
+          <t>✕</t>
+        </is>
+      </c>
+      <c r="C72" s="61" t="inlineStr">
+        <is>
+          <t>✕</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="56" customHeight="1">
+      <c r="A74" s="27" t="inlineStr">
+        <is>
+          <t>선택 기준은 층고가 아니라 음원. 아파트·오피스텔은 층고가 대체로 정해져 있어 층고 기준 등급 구분은 실효 없음. 판단 기준은 바닥을 직접 가진하는가와 저역이 지배적인가. 엔드핀이 바닥에 꽂히는 현악기, 다리로 하중을 전달하는 그랜드피아노, 패드 타격이 바닥으로 전달되는 전자드럼은 M2. 야간 사용·아래층 민감도가 높은 경우도 M2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="56" customHeight="1">
+      <c r="A75" s="48" t="inlineStr">
+        <is>
+          <t>어쿠스틱 드럼과 서브우퍼는 M1·M2 모두 대응 불가. 킥 드럼은 40~60Hz 집중 + 페달의 물리적 바닥 가진으로 아파트 구조에서는 어떤 바닥 사양으로도 민원을 피하기 어려움. 해당 음원은 아파트가 아닌 현장에서 AC-F-L5 + 방식 B로 계획. 상담 단계에서 명확히 선을 그을 것.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="11" t="inlineStr">
+        <is>
+          <t>자재</t>
+        </is>
+      </c>
+      <c r="B77" s="12" t="n"/>
+      <c r="C77" s="12" t="n"/>
+      <c r="D77" s="12" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>규격</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="17" t="inlineStr">
+        <is>
+          <t>마블충진재 특마</t>
+        </is>
+      </c>
+      <c r="B79" s="17" t="inlineStr">
+        <is>
+          <t>110K · 50T · 420×1200</t>
+        </is>
+      </c>
+      <c r="C79" s="17" t="inlineStr">
+        <is>
+          <t>방진층. 커터 재단</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="17" t="inlineStr">
+        <is>
+          <t>은박 EPE</t>
+        </is>
+      </c>
+      <c r="B80" s="17" t="inlineStr">
+        <is>
+          <t>3T</t>
+        </is>
+      </c>
+      <c r="C80" s="17" t="inlineStr">
+        <is>
+          <t>슬래브 상부 전면</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="17" t="inlineStr">
+        <is>
+          <t>합판</t>
+        </is>
+      </c>
+      <c r="B81" s="17" t="inlineStr">
+        <is>
+          <t>12T</t>
+        </is>
+      </c>
+      <c r="C81" s="17" t="inlineStr">
+        <is>
+          <t>하부 1장</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="17" t="inlineStr">
+        <is>
+          <t>PB (파티클보드)</t>
+        </is>
+      </c>
+      <c r="B82" s="17" t="inlineStr">
+        <is>
+          <t>15T</t>
+        </is>
+      </c>
+      <c r="C82" s="17" t="inlineStr">
+        <is>
+          <t>2장. 벽 · 천장 공용</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="17" t="inlineStr">
+        <is>
+          <t>돌차음판</t>
+        </is>
+      </c>
+      <c r="B83" s="17" t="inlineStr">
+        <is>
+          <t>4T · 자체 점착</t>
+        </is>
+      </c>
+      <c r="C83" s="17" t="inlineStr">
+        <is>
+          <t>PB 사이</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="17" t="inlineStr">
+        <is>
+          <t>목공본드</t>
+        </is>
+      </c>
+      <c r="B84" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C84" s="17" t="inlineStr">
+        <is>
+          <t>판재 간 전면 도포</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="17" t="inlineStr">
+        <is>
+          <t>피스</t>
+        </is>
+      </c>
+      <c r="B85" s="17" t="inlineStr">
+        <is>
+          <t>3.9 × 25 / 3.9 × 32</t>
+        </is>
+      </c>
+      <c r="C85" s="17" t="inlineStr">
+        <is>
+          <t>38mm 이상 반입 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="17" t="inlineStr">
+        <is>
+          <t>강화마루</t>
+        </is>
+      </c>
+      <c r="B86" s="17" t="inlineStr">
+        <is>
+          <t>8T · 클릭</t>
+        </is>
+      </c>
+      <c r="C86" s="17" t="inlineStr">
+        <is>
+          <t>언더레이 포함</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="17" t="inlineStr">
+        <is>
+          <t>탄성 실란트</t>
+        </is>
+      </c>
+      <c r="B87" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C87" s="17" t="inlineStr">
+        <is>
+          <t>연변부. 경화형 퍼티 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="11" t="inlineStr">
+        <is>
+          <t>시공 순서</t>
+        </is>
+      </c>
+      <c r="B89" s="12" t="n"/>
+      <c r="C89" s="12" t="n"/>
+      <c r="D89" s="12" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>작업</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>확인사항</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B91" s="17" t="inlineStr">
+        <is>
+          <t>슬래브 청소</t>
+        </is>
+      </c>
+      <c r="C91" s="17" t="inlineStr">
+        <is>
+          <t>이물질 · 돌출부 제거</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B92" s="17" t="inlineStr">
+        <is>
+          <t>평탄도 확인</t>
+        </is>
+      </c>
+      <c r="C92" s="17" t="inlineStr">
+        <is>
+          <t>3m당 ±3mm 초과 시 레벨링 선행</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B93" s="17" t="inlineStr">
+        <is>
+          <t>은박 EPE 3T 포설</t>
+        </is>
+      </c>
+      <c r="C93" s="17" t="inlineStr">
+        <is>
+          <t>은박면 상향 · 이음부 테이프</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="B94" s="17" t="inlineStr">
+        <is>
+          <t>마블 특마 50T 포설</t>
+        </is>
+      </c>
+      <c r="C94" s="17" t="inlineStr">
+        <is>
+          <t>밀착 맞댐 · 압축 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="B95" s="17" t="inlineStr">
+        <is>
+          <t>연변 세워 올림</t>
+        </is>
+      </c>
+      <c r="C95" s="17" t="inlineStr">
+        <is>
+          <t>마감면 위 10mm까지 (AC-J-01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="B96" s="17" t="inlineStr">
+        <is>
+          <t>합판 12T</t>
+        </is>
+      </c>
+      <c r="C96" s="17" t="inlineStr">
+        <is>
+          <t>이 시점부터 합판 위로만 이동</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="B97" s="17" t="inlineStr">
+        <is>
+          <t>본드 도포 · PB 15T</t>
+        </is>
+      </c>
+      <c r="C97" s="17" t="inlineStr">
+        <is>
+          <t>3~4㎡ 구간 분할 · 피스 3.9×25</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="B98" s="17" t="inlineStr">
+        <is>
+          <t>돌차음판 4T 부착</t>
+        </is>
+      </c>
+      <c r="C98" s="17" t="inlineStr">
+        <is>
+          <t>이형지 20~30cm씩 벗기며 밀착</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="18" t="n">
+        <v>9</v>
+      </c>
+      <c r="B99" s="17" t="inlineStr">
+        <is>
+          <t>본드 도포 · PB 15T</t>
+        </is>
+      </c>
+      <c r="C99" s="17" t="inlineStr">
+        <is>
+          <t>이음선 엇갈림 · 피스 3.9×32</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="B100" s="17" t="inlineStr">
+        <is>
+          <t>안정화</t>
+        </is>
+      </c>
+      <c r="C100" s="17" t="inlineStr">
+        <is>
+          <t>초기 침하 확인. 수일 경과 후 마감</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="B101" s="17" t="inlineStr">
+        <is>
+          <t>강화마루</t>
+        </is>
+      </c>
+      <c r="C101" s="17" t="inlineStr">
+        <is>
+          <t>클릭 부동 · 벽에서 8~10mm 이격</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="18" t="n">
+        <v>12</v>
+      </c>
+      <c r="B102" s="17" t="inlineStr">
+        <is>
+          <t>연변 정리 · 걸레받이</t>
+        </is>
+      </c>
+      <c r="C102" s="17" t="inlineStr">
+        <is>
+          <t>걸레받이는 라프트에만 고정</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
+          <t>시공상 유의사항</t>
+        </is>
+      </c>
+      <c r="B104" s="12" t="n"/>
+      <c r="C104" s="12" t="n"/>
+      <c r="D104" s="12" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="17" t="inlineStr">
+        <is>
+          <t>본드가 주력</t>
+        </is>
+      </c>
+      <c r="B106" s="17" t="inlineStr">
+        <is>
+          <t>PB는 나사 유지력이 합판의 60~70%. 목공본드 전면 도포, 피스는 압착 보조. 3~4㎡ 구간 분할</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="17" t="inlineStr">
+        <is>
+          <t>피스 길이</t>
+        </is>
+      </c>
+      <c r="B107" s="17" t="inlineStr">
+        <is>
+          <t>상부 PB→중간 PB는 3.9×32, 중간 PB→합판은 3.9×25. 마블 관통 절대 금지. 32mm 이하만 반입</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="17" t="inlineStr">
+        <is>
+          <t>마블 압축 금지</t>
+        </is>
+      </c>
+      <c r="B108" s="17" t="inlineStr">
+        <is>
+          <t>50T 그대로 유지. 420×1200 판재를 억지로 밀어 넣지 말고 커터로 재단</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="17" t="inlineStr">
+        <is>
+          <t>보행 관리</t>
+        </is>
+      </c>
+      <c r="B109" s="17" t="inlineStr">
+        <is>
+          <t>마블 직접 보행 금지. 합판을 순차 포설하며 그 위로 이동. 자재 적재 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="17" t="inlineStr">
+        <is>
+          <t>이음선 엇갈림</t>
+        </is>
+      </c>
+      <c r="B110" s="17" t="inlineStr">
+        <is>
+          <t>합판·PB·PB 이음선 300mm 이상 어긋나게. 상부 PB는 중간 PB와 직각 방향</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="17" t="inlineStr">
+        <is>
+          <t>강화마루 평탄도</t>
+        </is>
+      </c>
+      <c r="B111" s="17" t="inlineStr">
+        <is>
+          <t>클릭 조인트는 단차에 약함. 상부 PB 이음부 단차 3mm 이내 관리</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="17" t="inlineStr">
+        <is>
+          <t>연변 이격</t>
+        </is>
+      </c>
+      <c r="B112" s="17" t="inlineStr">
+        <is>
+          <t>라프트 전체 비접촉. 마루는 벽에서 8~10mm 이격 후 걸레받이로 덮되 걸레받이는 라프트에만 고정</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="17" t="inlineStr">
+        <is>
+          <t>중량물 구역</t>
+        </is>
+      </c>
+      <c r="B113" s="17" t="inlineStr">
+        <is>
+          <t>업라이트 피아노 등은 하중분산판(합판 18T 이상) 병용. 재생폼은 점하중 국부 압착에 취약</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="17" t="inlineStr">
+        <is>
+          <t>바닥은 피스만</t>
+        </is>
+      </c>
+      <c r="B114" s="17" t="inlineStr">
+        <is>
+          <t>스테이플 타카는 핀이 삐져나와 삐걱임 유발. 전 등급 공통 원칙</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="17" t="inlineStr">
+        <is>
+          <t>거주 중 시공</t>
+        </is>
+      </c>
+      <c r="B115" s="17" t="inlineStr">
+        <is>
+          <t>마블은 커터 재단이라 분진 거의 없음. PB 절단 시 톱밥 발생 — 집진 대책 준비</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="11" t="inlineStr">
+        <is>
+          <t>금지사항</t>
+        </is>
+      </c>
+      <c r="B117" s="12" t="n"/>
+      <c r="C117" s="12" t="n"/>
+      <c r="D117" s="12" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
         <is>
           <t>금지</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B118" s="3" t="inlineStr">
         <is>
           <t>사유</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="19" t="inlineStr"/>
-      <c r="B56" s="19" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="19" t="inlineStr"/>
-      <c r="B57" s="19" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="19" t="inlineStr"/>
-      <c r="B58" s="19" t="inlineStr"/>
+    <row r="119">
+      <c r="A119" s="28" t="inlineStr">
+        <is>
+          <t>마블 관통 피스</t>
+        </is>
+      </c>
+      <c r="B119" s="28" t="inlineStr">
+        <is>
+          <t>방진층 손상 · 슬래브 접촉 시 브릿지</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="28" t="inlineStr">
+        <is>
+          <t>스테이플 타카 사용</t>
+        </is>
+      </c>
+      <c r="B120" s="28" t="inlineStr">
+        <is>
+          <t>핀이 삐져나와 삐걱임 유발 — 바닥은 피스만</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="28" t="inlineStr">
+        <is>
+          <t>마블 압축 시공</t>
+        </is>
+      </c>
+      <c r="B121" s="28" t="inlineStr">
+        <is>
+          <t>동적강성 급등 · 방진 성능 상실</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="28" t="inlineStr">
+        <is>
+          <t>마블 직접 보행 · 적재</t>
+        </is>
+      </c>
+      <c r="B122" s="28" t="inlineStr">
+        <is>
+          <t>국부 압착</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="28" t="inlineStr">
+        <is>
+          <t>하부판을 PB로 대체</t>
+        </is>
+      </c>
+      <c r="B123" s="28" t="inlineStr">
+        <is>
+          <t>강성 부족 · 습기 취약 — 합판 유지</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="28" t="inlineStr">
+        <is>
+          <t>접착식 마감재 사용</t>
+        </is>
+      </c>
+      <c r="B124" s="28" t="inlineStr">
+        <is>
+          <t>연변 이격 파괴 · 침하 추종 불가 — 클릭 부동 마감</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="28" t="inlineStr">
+        <is>
+          <t>연변 이격 생략</t>
+        </is>
+      </c>
+      <c r="B125" s="28" t="inlineStr">
+        <is>
+          <t>측면전달음 발생</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="28" t="inlineStr">
+        <is>
+          <t>저역 음원 현장 적용</t>
+        </is>
+      </c>
+      <c r="B126" s="28" t="inlineStr">
+        <is>
+          <t>드럼 · 앰프 · 서브우퍼는 아파트에서 대응 불가</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="28" t="inlineStr">
+        <is>
+          <t>추정 성능 대외 기재</t>
+        </is>
+      </c>
+      <c r="B127" s="28" t="inlineStr">
+        <is>
+          <t>재생폼 압축 데이터 미확보</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A75:D75"/>
+    <mergeCell ref="A74:D74"/>
+    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="A52:D52"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A60:D60"/>
+    <mergeCell ref="A36:D36"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9216,290 +11605,1604 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:D134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="20" t="inlineStr">
-        <is>
-          <t>도면번호 체계</t>
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>AC-F-M2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>아파트형 부유바닥 · 더블레이어</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="inlineStr">
-        <is>
-          <t>AC - F - L0 - 01</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>접두어 - 부위 - 등급 - 세부</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Residential floating floor / dual resilient layer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>메타</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="n"/>
+      <c r="C5" s="12" t="n"/>
+      <c r="D5" s="12" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="22" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>부위</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>바닥 Floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>유형</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>총 두께</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>162 mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>분류</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>차음 (2단 절연)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>적용 현장</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>아파트 · 오피스텔</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>개정</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>M1 → M2 설계 논리</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n"/>
+      <c r="C13" s="12" t="n"/>
+      <c r="D13" s="12" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>효과</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="57" t="inlineStr">
+        <is>
+          <t>① 스프링 1개 → 2개</t>
+        </is>
+      </c>
+      <c r="B15" s="57" t="inlineStr">
+        <is>
+          <t>질량 3 · 스프링 2 구조</t>
+        </is>
+      </c>
+      <c r="C15" s="57" t="inlineStr">
+        <is>
+          <t>첫 공진 하향 + 상위 대역 감쇠 기울기 증가</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="57" t="inlineStr">
+        <is>
+          <t>② 하중에 맞춘 밀도 배분</t>
+        </is>
+      </c>
+      <c r="B16" s="57" t="inlineStr">
+        <is>
+          <t>하부 특마 110K(51 부담) / 상부 중마 70K(34 부담)</t>
+        </is>
+      </c>
+      <c r="C16" s="57" t="inlineStr">
+        <is>
+          <t>두 공진이 벌어져 딥 완만화</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="57" t="inlineStr">
+        <is>
+          <t>③ 비대칭 질량 배분</t>
+        </is>
+      </c>
+      <c r="B17" s="57" t="inlineStr">
+        <is>
+          <t>중간 17 / 상부 34 kg/㎡</t>
+        </is>
+      </c>
+      <c r="C17" s="57" t="inlineStr">
+        <is>
+          <t>대칭이면 두 공진 근접 — 불리</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="58" t="inlineStr">
+        <is>
+          <t>스프링을 직렬로 두는 것이 항상 유리하지 않음: 질량 3개가 되면 공진 모드도 2개. 첫 공진은 M1보다 내려가고 두 번째 공진 위로는 감쇠가 가팔라지나 두 공진 사이에 딥이 생김. 이 딥을 완만하게 만들기 위해 두 스프링 밀도(110K/70K)와 두 질량(17/34)을 모두 비대칭 배분. 대칭 구성은 두 공진이 근접해 오히려 불리.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>사양</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="n"/>
+      <c r="C21" s="12" t="n"/>
+      <c r="D21" s="12" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>명칭</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>아파트형 부유바닥 · 더블레이어</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>총 두께</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>162 mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>구성</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>은박 EPE 3T + 마블 특마 50T + 합판 12T + PB 15T + 마블 중마 50T + PB 15T + 돌차음판 4T + PB 15T + 강화마루 8T</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="59" t="inlineStr">
+        <is>
+          <t>방진층 1 (하부)</t>
+        </is>
+      </c>
+      <c r="B25" s="60" t="inlineStr">
+        <is>
+          <t>마블 특마 110K · 50T</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="59" t="inlineStr">
+        <is>
+          <t>방진층 2 (상부)</t>
+        </is>
+      </c>
+      <c r="B26" s="60" t="inlineStr">
+        <is>
+          <t>마블 중마 70K · 50T</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>중간 라프트</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>합판 12T + PB 15T · 약 17 kg/㎡</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>상부 라프트</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>PB 15T + 돌차음판 4T + PB 15T + 마루 · 약 34 kg/㎡</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>체결</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>목공본드 + 피스 3.9×25 / 3.9×32 · 라프트별 독립</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>마감</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>강화마루 클릭 부동 시공</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>대응</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>첼로 · 콘트라베이스 · 그랜드피아노 · 전자드럼 · 소출력 앰프 · 야간 사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="35" t="inlineStr">
+        <is>
+          <t>비대응</t>
+        </is>
+      </c>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>어쿠스틱 드럼 · 서브우퍼 (아파트에서 대응 불가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>적용</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>아파트 · 오피스텔 — 바닥 직접 가진 음원 또는 저역 지배 음원</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>질량 배분</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="n"/>
+      <c r="C35" s="12" t="n"/>
+      <c r="D35" s="12" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
-        <is>
-          <t>코드</t>
-        </is>
-      </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>구성</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>면밀도</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>부담 스프링</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="17" t="inlineStr">
+        <is>
+          <t>상부 라프트 M3</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="inlineStr">
+        <is>
+          <t>마루 8 + PB 15 + 돌판 4 + PB 15</t>
+        </is>
+      </c>
+      <c r="C37" s="17" t="inlineStr">
+        <is>
+          <t>약 34 kg/㎡</t>
+        </is>
+      </c>
+      <c r="D37" s="17" t="inlineStr">
+        <is>
+          <t>S2 (중마)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="17" t="inlineStr">
+        <is>
+          <t>중간 라프트 M2</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="inlineStr">
+        <is>
+          <t>PB 15 + 합판 12</t>
+        </is>
+      </c>
+      <c r="C38" s="17" t="inlineStr">
+        <is>
+          <t>약 17 kg/㎡</t>
+        </is>
+      </c>
+      <c r="D38" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="17" t="inlineStr">
+        <is>
+          <t>S1 부담 하중</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="inlineStr">
+        <is>
+          <t>M2 + M3</t>
+        </is>
+      </c>
+      <c r="C39" s="17" t="inlineStr">
+        <is>
+          <t>약 51 kg/㎡</t>
+        </is>
+      </c>
+      <c r="D39" s="17" t="inlineStr">
+        <is>
+          <t>S1 (특마)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="58" customHeight="1">
+      <c r="A41" s="27" t="inlineStr">
+        <is>
+          <t>하부 스프링이 두 배 이상의 하중을 받음: S2는 상부 라프트(34)만 지지하나 S1은 중간과 상부를 모두(51) 받음. 따라서 하부에 단단한 특마(110K), 상부에 무른 중마(70K)를 배치하는 것이 하중 배분에 맞음. 반대로 하면 하부가 과압축되어 바닥칠 위험 증가.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="58" customHeight="1">
+      <c r="A43" s="27" t="inlineStr">
+        <is>
+          <t>중간 라프트를 가볍게 두는 이유: 중간이 무거워지면 두 공진주파수가 근접해 그 사이 딥이 깊고 좁아짐. 중간은 합판+PB 최소 구성(17)으로 두고 질량을 상부(34)에 몰아 공진 간격을 벌림. 상부에 돌차음판을 배치한 것도 같은 이유.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>방진층 · 은박 EPE</t>
+        </is>
+      </c>
+      <c r="B45" s="12" t="n"/>
+      <c r="C45" s="12" t="n"/>
+      <c r="D45" s="12" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>하부 S1</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>상부 S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="17" t="inlineStr">
+        <is>
+          <t>제품</t>
+        </is>
+      </c>
+      <c r="B47" s="17" t="inlineStr">
+        <is>
+          <t>마블 특마</t>
+        </is>
+      </c>
+      <c r="C47" s="17" t="inlineStr">
+        <is>
+          <t>마블 중마</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="17" t="inlineStr">
+        <is>
+          <t>밀도</t>
+        </is>
+      </c>
+      <c r="B48" s="17" t="inlineStr">
+        <is>
+          <t>110 kg/㎥</t>
+        </is>
+      </c>
+      <c r="C48" s="17" t="inlineStr">
+        <is>
+          <t>70 kg/㎥</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="17" t="inlineStr">
+        <is>
+          <t>두께</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="inlineStr">
+        <is>
+          <t>50T</t>
+        </is>
+      </c>
+      <c r="C49" s="17" t="inlineStr">
+        <is>
+          <t>50T</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="17" t="inlineStr">
+        <is>
+          <t>부담 하중</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="inlineStr">
+        <is>
+          <t>약 51 kg/㎡</t>
+        </is>
+      </c>
+      <c r="C50" s="17" t="inlineStr">
+        <is>
+          <t>약 34 kg/㎡</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="28" t="inlineStr">
+        <is>
+          <t>동탄성계수</t>
+        </is>
+      </c>
+      <c r="B51" s="28" t="inlineStr">
+        <is>
+          <t>데이터 미확보</t>
+        </is>
+      </c>
+      <c r="C51" s="28" t="inlineStr">
+        <is>
+          <t>데이터 미확보</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="28" t="inlineStr">
+        <is>
+          <t>압축영구변형률</t>
+        </is>
+      </c>
+      <c r="B52" s="28" t="inlineStr">
+        <is>
+          <t>데이터 미확보</t>
+        </is>
+      </c>
+      <c r="C52" s="28" t="inlineStr">
+        <is>
+          <t>데이터 미확보</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="58" customHeight="1">
+      <c r="A54" s="48" t="inlineStr">
+        <is>
+          <t>재생폼 데이터 미확보 — 선결 과제: M2는 하부 스프링이 51 kg/㎡를 받으므로 M1(41)보다 압축 조건이 가혹. 하중 4~5kPa에서의 압축률과 압축영구변형률 확보 전까지 성능 수치를 대외 자료에 기재하지 않음. 중마 70K는 특마보다 무르므로 상부 국부 하중(가구 다리 등)에 대한 확인이 특히 필요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="58" customHeight="1">
+      <c r="A56" s="56" t="inlineStr">
+        <is>
+          <t>은박 EPE 3T는 M1과 동일: 슬래브 상부 전면 포설하여 폼이 슬래브에 직접 닿지 않게 함. 단열이 목적이 아니라 접촉 완충 · 방습 · 요철 흡수가 목적.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>바닥난방 안내</t>
+        </is>
+      </c>
+      <c r="B58" s="12" t="n"/>
+      <c r="C58" s="12" t="n"/>
+      <c r="D58" s="12" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="13" t="inlineStr">
+        <is>
+          <t>난방 효율</t>
+        </is>
+      </c>
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t>M1보다 열저항이 커 온돌 난방이 사실상 전달되지 않음</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="13" t="inlineStr">
+        <is>
+          <t>권장</t>
+        </is>
+      </c>
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t>냉난방 겸용 에어컨 등 별도 냉난방 계획</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="13" t="inlineStr">
+        <is>
+          <t>온돌 유지 시</t>
+        </is>
+      </c>
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t>저온 운전 권장</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="13" t="inlineStr">
+        <is>
+          <t>사전 협의</t>
+        </is>
+      </c>
+      <c r="B62" s="14" t="inlineStr">
+        <is>
+          <t>계약 단계에서 명확히 고지</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t>M1 · M2 선택 기준</t>
+        </is>
+      </c>
+      <c r="B64" s="12" t="n"/>
+      <c r="C64" s="12" t="n"/>
+      <c r="D64" s="12" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>조건</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="17" t="inlineStr">
+        <is>
+          <t>바이올린 · 비올라 · 관악 · 성악</t>
+        </is>
+      </c>
+      <c r="B66" s="18" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C66" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="17" t="inlineStr">
+        <is>
+          <t>업라이트 피아노</t>
+        </is>
+      </c>
+      <c r="B67" s="18" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C67" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="17" t="inlineStr">
+        <is>
+          <t>소출력 모니터 · 헤드폰 작업</t>
+        </is>
+      </c>
+      <c r="B68" s="18" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C68" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="17" t="inlineStr">
+        <is>
+          <t>첼로 · 콘트라베이스 (엔드핀 바닥 가진)</t>
+        </is>
+      </c>
+      <c r="B69" s="18" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="C69" s="18" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="17" t="inlineStr">
+        <is>
+          <t>그랜드피아노 (다리 하중 · 저역)</t>
+        </is>
+      </c>
+      <c r="B70" s="18" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="C70" s="18" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="17" t="inlineStr">
+        <is>
+          <t>전자드럼 (패드 타격)</t>
+        </is>
+      </c>
+      <c r="B71" s="18" t="inlineStr">
+        <is>
+          <t>✕</t>
+        </is>
+      </c>
+      <c r="C71" s="18" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="17" t="inlineStr">
+        <is>
+          <t>기타 · 베이스 앰프 (소출력)</t>
+        </is>
+      </c>
+      <c r="B72" s="18" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="C72" s="18" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="17" t="inlineStr">
+        <is>
+          <t>야간 사용 · 아래층 민감</t>
+        </is>
+      </c>
+      <c r="B73" s="18" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="C73" s="18" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="28" t="inlineStr">
+        <is>
+          <t>어쿠스틱 드럼 · 서브우퍼</t>
+        </is>
+      </c>
+      <c r="B74" s="61" t="inlineStr">
+        <is>
+          <t>✕</t>
+        </is>
+      </c>
+      <c r="C74" s="61" t="inlineStr">
+        <is>
+          <t>✕</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="56" customHeight="1">
+      <c r="A76" s="27" t="inlineStr">
+        <is>
+          <t>선택 기준은 층고가 아니라 음원. 아파트·오피스텔은 층고가 대체로 정해져 있어 층고 기준 등급 구분은 실효 없음. 판단 기준은 바닥을 직접 가진하는가와 저역이 지배적인가. 엔드핀이 바닥에 꽂히는 현악기, 다리로 하중을 전달하는 그랜드피아노, 패드 타격이 바닥으로 전달되는 전자드럼은 M2. 야간 사용·아래층 민감도가 높은 경우도 M2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="56" customHeight="1">
+      <c r="A77" s="48" t="inlineStr">
+        <is>
+          <t>어쿠스틱 드럼과 서브우퍼는 M1·M2 모두 대응 불가. 킥 드럼은 40~60Hz 집중 + 페달의 물리적 바닥 가진으로 아파트 구조에서는 어떤 바닥 사양으로도 민원을 피하기 어려움. 해당 음원은 아파트가 아닌 현장에서 AC-F-L5 + 방식 B로 계획. 상담 단계에서 명확히 선을 그을 것.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="11" t="inlineStr">
+        <is>
+          <t>자재</t>
+        </is>
+      </c>
+      <c r="B79" s="12" t="n"/>
+      <c r="C79" s="12" t="n"/>
+      <c r="D79" s="12" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>규격</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="57" t="inlineStr">
+        <is>
+          <t>마블충진재 특마</t>
+        </is>
+      </c>
+      <c r="B81" s="57" t="inlineStr">
+        <is>
+          <t>110K · 50T · 420×1200</t>
+        </is>
+      </c>
+      <c r="C81" s="57" t="inlineStr">
+        <is>
+          <t>하부 방진층 S1</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="57" t="inlineStr">
+        <is>
+          <t>마블충진재 중마</t>
+        </is>
+      </c>
+      <c r="B82" s="57" t="inlineStr">
+        <is>
+          <t>70K · 50T · 420×1200</t>
+        </is>
+      </c>
+      <c r="C82" s="57" t="inlineStr">
+        <is>
+          <t>상부 방진층 S2. 벽 · 천장 공용</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="17" t="inlineStr">
+        <is>
+          <t>은박 EPE</t>
+        </is>
+      </c>
+      <c r="B83" s="17" t="inlineStr">
+        <is>
+          <t>3T</t>
+        </is>
+      </c>
+      <c r="C83" s="17" t="inlineStr">
+        <is>
+          <t>슬래브 상부 전면</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="17" t="inlineStr">
+        <is>
+          <t>합판</t>
+        </is>
+      </c>
+      <c r="B84" s="17" t="inlineStr">
+        <is>
+          <t>12T</t>
+        </is>
+      </c>
+      <c r="C84" s="17" t="inlineStr">
+        <is>
+          <t>중간 라프트 하부 1장</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="17" t="inlineStr">
+        <is>
+          <t>PB (파티클보드)</t>
+        </is>
+      </c>
+      <c r="B85" s="17" t="inlineStr">
+        <is>
+          <t>15T</t>
+        </is>
+      </c>
+      <c r="C85" s="17" t="inlineStr">
+        <is>
+          <t>3장. 벽 · 천장 공용</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="17" t="inlineStr">
+        <is>
+          <t>돌차음판</t>
+        </is>
+      </c>
+      <c r="B86" s="17" t="inlineStr">
+        <is>
+          <t>4T · 자체 점착</t>
+        </is>
+      </c>
+      <c r="C86" s="17" t="inlineStr">
+        <is>
+          <t>상부 라프트 내부</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="17" t="inlineStr">
+        <is>
+          <t>목공본드</t>
+        </is>
+      </c>
+      <c r="B87" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C87" s="17" t="inlineStr">
+        <is>
+          <t>판재 간 전면 도포</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="17" t="inlineStr">
+        <is>
+          <t>피스</t>
+        </is>
+      </c>
+      <c r="B88" s="17" t="inlineStr">
+        <is>
+          <t>3.9 × 25 / 3.9 × 32</t>
+        </is>
+      </c>
+      <c r="C88" s="17" t="inlineStr">
+        <is>
+          <t>38mm 이상 반입 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="17" t="inlineStr">
+        <is>
+          <t>강화마루</t>
+        </is>
+      </c>
+      <c r="B89" s="17" t="inlineStr">
+        <is>
+          <t>8T · 클릭</t>
+        </is>
+      </c>
+      <c r="C89" s="17" t="inlineStr">
+        <is>
+          <t>언더레이 포함</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="17" t="inlineStr">
+        <is>
+          <t>탄성 실란트</t>
+        </is>
+      </c>
+      <c r="B90" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C90" s="17" t="inlineStr">
+        <is>
+          <t>연변부. 경화형 퍼티 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="11" t="inlineStr">
+        <is>
+          <t>시공 순서</t>
+        </is>
+      </c>
+      <c r="B92" s="12" t="n"/>
+      <c r="C92" s="12" t="n"/>
+      <c r="D92" s="12" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>작업</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>확인사항</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B94" s="17" t="inlineStr">
+        <is>
+          <t>슬래브 청소 · 평탄도 확인</t>
+        </is>
+      </c>
+      <c r="C94" s="17" t="inlineStr">
+        <is>
+          <t>3m당 ±3mm 초과 시 레벨링 선행</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B95" s="17" t="inlineStr">
+        <is>
+          <t>은박 EPE 3T 포설</t>
+        </is>
+      </c>
+      <c r="C95" s="17" t="inlineStr">
+        <is>
+          <t>은박면 상향 · 이음부 테이프</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B96" s="17" t="inlineStr">
+        <is>
+          <t>마블 특마 50T 포설</t>
+        </is>
+      </c>
+      <c r="C96" s="17" t="inlineStr">
+        <is>
+          <t>밀착 맞댐 · 압축 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="B97" s="17" t="inlineStr">
+        <is>
+          <t>연변 세워 올림 (1차)</t>
+        </is>
+      </c>
+      <c r="C97" s="17" t="inlineStr">
+        <is>
+          <t>중간 라프트 높이까지</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="B98" s="17" t="inlineStr">
+        <is>
+          <t>합판 12T</t>
+        </is>
+      </c>
+      <c r="C98" s="17" t="inlineStr">
+        <is>
+          <t>이 시점부터 합판 위로만 이동</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="B99" s="17" t="inlineStr">
+        <is>
+          <t>본드 도포 · PB 15T</t>
+        </is>
+      </c>
+      <c r="C99" s="17" t="inlineStr">
+        <is>
+          <t>피스 3.9×25 · 중간 라프트 완성</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="B100" s="17" t="inlineStr">
+        <is>
+          <t>마블 중마 50T 포설</t>
+        </is>
+      </c>
+      <c r="C100" s="17" t="inlineStr">
+        <is>
+          <t>밀착 맞댐 · 압축 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="B101" s="17" t="inlineStr">
+        <is>
+          <t>연변 세워 올림 (2차)</t>
+        </is>
+      </c>
+      <c r="C101" s="17" t="inlineStr">
+        <is>
+          <t>마감면 위 10mm까지 (AC-J-01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="18" t="n">
+        <v>9</v>
+      </c>
+      <c r="B102" s="17" t="inlineStr">
+        <is>
+          <t>PB 15T</t>
+        </is>
+      </c>
+      <c r="C102" s="17" t="inlineStr">
+        <is>
+          <t>중마 위에 얹음 · 하부와 연결 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="B103" s="17" t="inlineStr">
+        <is>
+          <t>돌차음판 4T 부착</t>
+        </is>
+      </c>
+      <c r="C103" s="17" t="inlineStr">
+        <is>
+          <t>이형지 20~30cm씩 벗기며 밀착</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="B104" s="17" t="inlineStr">
+        <is>
+          <t>본드 도포 · PB 15T</t>
+        </is>
+      </c>
+      <c r="C104" s="17" t="inlineStr">
+        <is>
+          <t>피스 3.9×32 · 상부 라프트 완성</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="18" t="n">
+        <v>12</v>
+      </c>
+      <c r="B105" s="17" t="inlineStr">
+        <is>
+          <t>안정화</t>
+        </is>
+      </c>
+      <c r="C105" s="17" t="inlineStr">
+        <is>
+          <t>초기 침하 확인. 수일 경과 후 마감</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="18" t="n">
+        <v>13</v>
+      </c>
+      <c r="B106" s="17" t="inlineStr">
+        <is>
+          <t>강화마루</t>
+        </is>
+      </c>
+      <c r="C106" s="17" t="inlineStr">
+        <is>
+          <t>클릭 부동 · 벽에서 8~10mm 이격</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="18" t="n">
+        <v>14</v>
+      </c>
+      <c r="B107" s="17" t="inlineStr">
+        <is>
+          <t>연변 정리 · 걸레받이</t>
+        </is>
+      </c>
+      <c r="C107" s="17" t="inlineStr">
+        <is>
+          <t>걸레받이는 상부 라프트에만 고정</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="11" t="inlineStr">
+        <is>
+          <t>시공상 유의사항</t>
+        </is>
+      </c>
+      <c r="B109" s="12" t="n"/>
+      <c r="C109" s="12" t="n"/>
+      <c r="D109" s="12" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
         <is>
           <t>내용</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="23" t="inlineStr">
-        <is>
-          <t>접두어</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="C7" s="23" t="inlineStr">
-        <is>
-          <t>Acoustic — 전 도면 공통</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="23" t="inlineStr">
-        <is>
-          <t>부위</t>
-        </is>
-      </c>
-      <c r="B8" s="23" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C8" s="23" t="inlineStr">
-        <is>
-          <t>바닥 Floor</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="23" t="inlineStr">
-        <is>
-          <t>부위</t>
-        </is>
-      </c>
-      <c r="B9" s="23" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="C9" s="23" t="inlineStr">
-        <is>
-          <t>벽 Wall</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="23" t="inlineStr">
-        <is>
-          <t>부위</t>
-        </is>
-      </c>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C10" s="23" t="inlineStr">
-        <is>
-          <t>천장 Ceiling</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="23" t="inlineStr">
-        <is>
-          <t>부위</t>
-        </is>
-      </c>
-      <c r="B11" s="23" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C11" s="23" t="inlineStr">
-        <is>
-          <t>문 Door</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="23" t="inlineStr">
-        <is>
-          <t>부위</t>
-        </is>
-      </c>
-      <c r="B12" s="23" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="C12" s="23" t="inlineStr">
-        <is>
-          <t>창 Glazing</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="23" t="inlineStr">
-        <is>
-          <t>부위</t>
-        </is>
-      </c>
-      <c r="B13" s="23" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="C13" s="23" t="inlineStr">
-        <is>
-          <t>설비 Mechanical (덕트 · 환기)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="23" t="inlineStr">
-        <is>
-          <t>부위</t>
-        </is>
-      </c>
-      <c r="B14" s="23" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="C14" s="23" t="inlineStr">
-        <is>
-          <t>접합부 Joint — 등급 무관 공통 상세</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="23" t="inlineStr">
-        <is>
-          <t>등급</t>
-        </is>
-      </c>
-      <c r="B15" s="23" t="inlineStr">
-        <is>
-          <t>L0~L5</t>
-        </is>
-      </c>
-      <c r="C15" s="23" t="inlineStr">
-        <is>
-          <t>성능 등급 (한 자리)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="23" t="inlineStr">
-        <is>
-          <t>세부</t>
-        </is>
-      </c>
-      <c r="B16" s="23" t="inlineStr">
-        <is>
-          <t>-01, -02</t>
-        </is>
-      </c>
-      <c r="C16" s="23" t="inlineStr">
-        <is>
-          <t>부분 상세 (필요 시)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="24" t="inlineStr">
-        <is>
-          <t>J 시리즈 예시</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="24" t="inlineStr">
-        <is>
-          <t>AC-J-01</t>
-        </is>
-      </c>
-      <c r="B19" s="25" t="inlineStr">
-        <is>
-          <t>연변 이격 상세 (Perimeter isolation)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="24" t="inlineStr">
-        <is>
-          <t>AC-J-02</t>
-        </is>
-      </c>
-      <c r="B20" s="25" t="inlineStr">
-        <is>
-          <t>문턱 · 출입구 접합</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="24" t="inlineStr">
-        <is>
-          <t>AC-J-03</t>
-        </is>
-      </c>
-      <c r="B21" s="25" t="inlineStr">
-        <is>
-          <t>관통부 방진 슬리브 (배관 · 전기)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="24" t="inlineStr">
-        <is>
-          <t>AC-J-04</t>
-        </is>
-      </c>
-      <c r="B22" s="25" t="inlineStr">
-        <is>
-          <t>벽 하부 접합 — 방식 A (벽 선시공)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="24" t="inlineStr">
-        <is>
-          <t>AC-J-05</t>
-        </is>
-      </c>
-      <c r="B23" s="25" t="inlineStr">
-        <is>
-          <t>벽 하부 접합 — 방식 B (박스 인 박스)</t>
+    <row r="111">
+      <c r="A111" s="17" t="inlineStr">
+        <is>
+          <t>두 라프트를 연결하지 않음</t>
+        </is>
+      </c>
+      <c r="B111" s="17" t="inlineStr">
+        <is>
+          <t>M2의 핵심. 중간 라프트와 상부 라프트를 각각 독립적으로 묶고 중마 관통 피스 절대 금지. 하나라도 관통하면 두 스프링이 직결되어 M2가 M1으로 전락</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="17" t="inlineStr">
+        <is>
+          <t>피스 길이</t>
+        </is>
+      </c>
+      <c r="B112" s="17" t="inlineStr">
+        <is>
+          <t>중간 라프트 3.9×25(PB→합판), 상부 라프트 3.9×32(PB→돌판→PB). 32mm 이하만 반입</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="17" t="inlineStr">
+        <is>
+          <t>상부 라프트는 얹혀만 있음</t>
+        </is>
+      </c>
+      <c r="B113" s="17" t="inlineStr">
+        <is>
+          <t>중마 위 부동 상태. 시공 중이나 중량물 이동 시 밀릴 수 있음. 실사용에서는 자중(34)으로 안정되나 시공 중 위치 이탈 수시 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="17" t="inlineStr">
+        <is>
+          <t>본드가 주력</t>
+        </is>
+      </c>
+      <c r="B114" s="17" t="inlineStr">
+        <is>
+          <t>PB는 나사 유지력이 합판의 60~70%. 목공본드 전면 도포, 3~4㎡ 구간 분할</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="17" t="inlineStr">
+        <is>
+          <t>마블 압축 금지</t>
+        </is>
+      </c>
+      <c r="B115" s="17" t="inlineStr">
+        <is>
+          <t>특마·중마 모두 50T 그대로 유지. 억지로 밀어 넣지 말고 커터로 재단</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="17" t="inlineStr">
+        <is>
+          <t>보행 관리</t>
+        </is>
+      </c>
+      <c r="B116" s="17" t="inlineStr">
+        <is>
+          <t>마블 직접 보행 금지. 하부는 합판, 상부는 PB를 순차 포설하며 그 위로 이동</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="17" t="inlineStr">
+        <is>
+          <t>연변 이격 2단</t>
+        </is>
+      </c>
+      <c r="B117" s="17" t="inlineStr">
+        <is>
+          <t>중간 라프트와 상부 라프트 모두 벽에 닿지 않아야 함. 마블을 두 번 세워 올림</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="17" t="inlineStr">
+        <is>
+          <t>중량물 구역</t>
+        </is>
+      </c>
+      <c r="B118" s="17" t="inlineStr">
+        <is>
+          <t>중마 70K는 특마보다 무르므로 점하중에 더 취약. 피아노 등은 하중분산판 반드시 병용</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="17" t="inlineStr">
+        <is>
+          <t>강화마루 평탄도</t>
+        </is>
+      </c>
+      <c r="B119" s="17" t="inlineStr">
+        <is>
+          <t>클릭 조인트는 단차에 약함. 상부 PB 이음부 단차 3mm 이내 관리</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="17" t="inlineStr">
+        <is>
+          <t>바닥은 피스만</t>
+        </is>
+      </c>
+      <c r="B120" s="17" t="inlineStr">
+        <is>
+          <t>스테이플 타카 금지. 전 등급 공통 원칙</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="17" t="inlineStr">
+        <is>
+          <t>층고 검토</t>
+        </is>
+      </c>
+      <c r="B121" s="17" t="inlineStr">
+        <is>
+          <t>162mm는 M1(107) 대비 55mm 두꺼움. 천장 방음까지 계획한다면 실내 높이 사전 검토</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="11" t="inlineStr">
+        <is>
+          <t>금지사항</t>
+        </is>
+      </c>
+      <c r="B123" s="12" t="n"/>
+      <c r="C123" s="12" t="n"/>
+      <c r="D123" s="12" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>금지</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>사유</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="28" t="inlineStr">
+        <is>
+          <t>중마 관통 피스</t>
+        </is>
+      </c>
+      <c r="B125" s="28" t="inlineStr">
+        <is>
+          <t>두 스프링 직결 — M2 구조 무효화</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="28" t="inlineStr">
+        <is>
+          <t>두 라프트 연결 부재</t>
+        </is>
+      </c>
+      <c r="B126" s="28" t="inlineStr">
+        <is>
+          <t>어떤 부재로든 상하 라프트 연결 금지</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="28" t="inlineStr">
+        <is>
+          <t>특마 관통 피스</t>
+        </is>
+      </c>
+      <c r="B127" s="28" t="inlineStr">
+        <is>
+          <t>방진층 손상 · 슬래브 접촉 시 브릿지</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="28" t="inlineStr">
+        <is>
+          <t>스테이플 타카 사용</t>
+        </is>
+      </c>
+      <c r="B128" s="28" t="inlineStr">
+        <is>
+          <t>핀이 삐져나와 삐걱임 유발 — 바닥은 피스만</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="28" t="inlineStr">
+        <is>
+          <t>특마 · 중마 위치 반전</t>
+        </is>
+      </c>
+      <c r="B129" s="28" t="inlineStr">
+        <is>
+          <t>하부 과압축 · 바닥칠 위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="28" t="inlineStr">
+        <is>
+          <t>마블 압축 시공</t>
+        </is>
+      </c>
+      <c r="B130" s="28" t="inlineStr">
+        <is>
+          <t>동적강성 급등 · 방진 성능 상실</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="28" t="inlineStr">
+        <is>
+          <t>중간 라프트 질량 증대</t>
+        </is>
+      </c>
+      <c r="B131" s="28" t="inlineStr">
+        <is>
+          <t>두 공진 근접 — 딥 심화</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="28" t="inlineStr">
+        <is>
+          <t>접착식 마감재 사용</t>
+        </is>
+      </c>
+      <c r="B132" s="28" t="inlineStr">
+        <is>
+          <t>연변 이격 파괴 — 클릭 부동 마감</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="28" t="inlineStr">
+        <is>
+          <t>저역 음원 현장 적용</t>
+        </is>
+      </c>
+      <c r="B133" s="28" t="inlineStr">
+        <is>
+          <t>드럼 · 앰프 · 서브우퍼는 아파트에서 대응 불가</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="28" t="inlineStr">
+        <is>
+          <t>추정 성능 대외 기재</t>
+        </is>
+      </c>
+      <c r="B134" s="28" t="inlineStr">
+        <is>
+          <t>재생폼 압축 데이터 미확보</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A56:D56"/>
+    <mergeCell ref="A77:D77"/>
+    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A76:D76"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>